--- a/shabbatot/2026-09-04.xlsx
+++ b/shabbatot/2026-09-04.xlsx
@@ -12269,14 +12269,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -12299,15 +12300,20 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
+          <t>חבילת אחריות</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
           <t>חניכים (מחושב מגיליון «חניכים»)</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>ערכת צבע</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>מס' חניכים</t>
         </is>
@@ -12319,21 +12325,22 @@
           <t>קבוצה 1</t>
         </is>
       </c>
-      <c r="B3" s="86" t="inlineStr">
+      <c r="B3" s="86" t="n"/>
+      <c r="C3" s="69" t="inlineStr">
         <is>
           <t>קידוש ומאפים</t>
         </is>
       </c>
-      <c r="C3" s="87">
+      <c r="D3" s="87">
         <f>IF($A3="","",'חניכים'!$F$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D3" s="69" t="inlineStr">
+      <c r="E3" s="69" t="inlineStr">
         <is>
           <t>ורוד</t>
         </is>
       </c>
-      <c r="E3" s="88">
+      <c r="F3" s="88">
         <f>IF($A3="","",COUNTIF('חניכים'!$B$3:$B$132,$A3))</f>
         <v/>
       </c>
@@ -12344,21 +12351,22 @@
           <t>קבוצה 2</t>
         </is>
       </c>
-      <c r="B4" s="86" t="inlineStr">
+      <c r="B4" s="86" t="n"/>
+      <c r="C4" s="69" t="inlineStr">
         <is>
           <t>ארוחות שבת</t>
         </is>
       </c>
-      <c r="C4" s="87">
+      <c r="D4" s="87">
         <f>IF($A4="","",'חניכים'!$G$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D4" s="69" t="inlineStr">
+      <c r="E4" s="69" t="inlineStr">
         <is>
           <t>ים</t>
         </is>
       </c>
-      <c r="E4" s="88">
+      <c r="F4" s="88">
         <f>IF($A4="","",COUNTIF('חניכים'!$B$3:$B$132,$A4))</f>
         <v/>
       </c>
@@ -12369,21 +12377,22 @@
           <t>קבוצה 3</t>
         </is>
       </c>
-      <c r="B5" s="86" t="inlineStr">
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="69" t="inlineStr">
         <is>
           <t>ארוחות שישי וסעודה שלישית</t>
         </is>
       </c>
-      <c r="C5" s="87">
+      <c r="D5" s="87">
         <f>IF($A5="","",'חניכים'!$H$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D5" s="69" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>ספארי</t>
         </is>
       </c>
-      <c r="E5" s="88">
+      <c r="F5" s="88">
         <f>IF($A5="","",COUNTIF('חניכים'!$B$3:$B$132,$A5))</f>
         <v/>
       </c>
@@ -12394,21 +12403,22 @@
           <t>קבוצה 4</t>
         </is>
       </c>
-      <c r="B6" s="86" t="inlineStr">
+      <c r="B6" s="86" t="n"/>
+      <c r="C6" s="69" t="inlineStr">
         <is>
           <t>טיש ואחריות טכנית</t>
         </is>
       </c>
-      <c r="C6" s="87">
+      <c r="D6" s="87">
         <f>IF($A6="","",'חניכים'!$I$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D6" s="69" t="inlineStr">
+      <c r="E6" s="69" t="inlineStr">
         <is>
           <t>שדה</t>
         </is>
       </c>
-      <c r="E6" s="88">
+      <c r="F6" s="88">
         <f>IF($A6="","",COUNTIF('חניכים'!$B$3:$B$132,$A6))</f>
         <v/>
       </c>
@@ -12416,16 +12426,17 @@
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="80" t="n"/>
       <c r="B7" s="86" t="n"/>
-      <c r="C7" s="87">
+      <c r="C7" s="69" t="n"/>
+      <c r="D7" s="87">
         <f>IF($A7="","",'חניכים'!$J$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D7" s="69" t="inlineStr">
+      <c r="E7" s="69" t="inlineStr">
         <is>
           <t>סגול</t>
         </is>
       </c>
-      <c r="E7" s="88">
+      <c r="F7" s="88">
         <f>IF($A7="","",COUNTIF('חניכים'!$B$3:$B$132,$A7))</f>
         <v/>
       </c>
@@ -12433,16 +12444,17 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="80" t="n"/>
       <c r="B8" s="86" t="n"/>
-      <c r="C8" s="87">
+      <c r="C8" s="69" t="n"/>
+      <c r="D8" s="87">
         <f>IF($A8="","",'חניכים'!$K$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D8" s="69" t="inlineStr">
+      <c r="E8" s="69" t="inlineStr">
         <is>
           <t>ירוק</t>
         </is>
       </c>
-      <c r="E8" s="88">
+      <c r="F8" s="88">
         <f>IF($A8="","",COUNTIF('חניכים'!$B$3:$B$132,$A8))</f>
         <v/>
       </c>
@@ -12450,17 +12462,17 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>שמות הקבוצות והמובילים נקבעים כאן. רשימת החניכים מחושבת מגיליון «חניכים» — אין מה להקליד בה. ערכת הצבע קובעת את צבע הכרטיסייה.</t>
+          <t>שמות הקבוצות והמובילים נקבעים כאן. «חבילת אחריות» היא תחום האחריות של הקבוצה בשבת הזו. רשימת החניכים מחושבת מגיליון «חניכים» — אין מה להקליד בה. ערכת הצבע קובעת את צבע הכרטיסייה.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D3:D8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ורוד,ים,ספארי,שדה,סגול,ירוק"</formula1>
     </dataValidation>
   </dataValidations>
@@ -22825,7 +22837,7 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="26">
-        <f>IF('קבוצות'!$C$3="","",'קבוצות'!$C$3)</f>
+        <f>IF('קבוצות'!$D$3="","",'קבוצות'!$D$3)</f>
         <v/>
       </c>
     </row>
@@ -23651,7 +23663,7 @@
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="37">
-        <f>IF('קבוצות'!$C$4="","",'קבוצות'!$C$4)</f>
+        <f>IF('קבוצות'!$D$4="","",'קבוצות'!$D$4)</f>
         <v/>
       </c>
     </row>
@@ -24477,7 +24489,7 @@
     </row>
     <row r="52" ht="60" customHeight="1">
       <c r="A52" s="41">
-        <f>IF('קבוצות'!$C$5="","",'קבוצות'!$C$5)</f>
+        <f>IF('קבוצות'!$D$5="","",'קבוצות'!$D$5)</f>
         <v/>
       </c>
     </row>
@@ -25303,7 +25315,7 @@
     </row>
     <row r="77" ht="60" customHeight="1">
       <c r="A77" s="45">
-        <f>IF('קבוצות'!$C$6="","",'קבוצות'!$C$6)</f>
+        <f>IF('קבוצות'!$D$6="","",'קבוצות'!$D$6)</f>
         <v/>
       </c>
     </row>
@@ -26129,7 +26141,7 @@
     </row>
     <row r="102" ht="60" customHeight="1">
       <c r="A102" s="49">
-        <f>IF('קבוצות'!$C$7="","",'קבוצות'!$C$7)</f>
+        <f>IF('קבוצות'!$D$7="","",'קבוצות'!$D$7)</f>
         <v/>
       </c>
     </row>
@@ -26955,7 +26967,7 @@
     </row>
     <row r="127" ht="60" customHeight="1">
       <c r="A127" s="53">
-        <f>IF('קבוצות'!$C$8="","",'קבוצות'!$C$8)</f>
+        <f>IF('קבוצות'!$D$8="","",'קבוצות'!$D$8)</f>
         <v/>
       </c>
     </row>
@@ -27916,362 +27928,362 @@
   </mergeCells>
   <conditionalFormatting sqref="A2:F3">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>'קבוצות'!$D$3="ורוד"</formula>
+      <formula>'קבוצות'!$E$3="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="2">
-      <formula>'קבוצות'!$D$3="ים"</formula>
+      <formula>'קבוצות'!$E$3="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="3">
-      <formula>'קבוצות'!$D$3="ספארי"</formula>
+      <formula>'קבוצות'!$E$3="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="10" dxfId="4">
-      <formula>'קבוצות'!$D$3="שדה"</formula>
+      <formula>'קבוצות'!$E$3="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="13" dxfId="5">
-      <formula>'קבוצות'!$D$3="סגול"</formula>
+      <formula>'קבוצות'!$E$3="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="16" dxfId="6">
-      <formula>'קבוצות'!$D$3="ירוק"</formula>
+      <formula>'קבוצות'!$E$3="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A22">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>'קבוצות'!$D$3="ורוד"</formula>
+      <formula>'קבוצות'!$E$3="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="2">
-      <formula>'קבוצות'!$D$3="ים"</formula>
+      <formula>'קבוצות'!$E$3="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="3">
-      <formula>'קבוצות'!$D$3="ספארי"</formula>
+      <formula>'קבוצות'!$E$3="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="11" dxfId="4">
-      <formula>'קבוצות'!$D$3="שדה"</formula>
+      <formula>'קבוצות'!$E$3="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="14" dxfId="5">
-      <formula>'קבוצות'!$D$3="סגול"</formula>
+      <formula>'קבוצות'!$E$3="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="17" dxfId="6">
-      <formula>'קבוצות'!$D$3="ירוק"</formula>
+      <formula>'קבוצות'!$E$3="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:F1">
     <cfRule type="expression" priority="3" dxfId="7">
-      <formula>'קבוצות'!$D$3="ורוד"</formula>
+      <formula>'קבוצות'!$E$3="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="8">
-      <formula>'קבוצות'!$D$3="ים"</formula>
+      <formula>'קבוצות'!$E$3="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="9">
-      <formula>'קבוצות'!$D$3="ספארי"</formula>
+      <formula>'קבוצות'!$E$3="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="12" dxfId="10">
-      <formula>'קבוצות'!$D$3="שדה"</formula>
+      <formula>'קבוצות'!$E$3="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="15" dxfId="11">
-      <formula>'קבוצות'!$D$3="סגול"</formula>
+      <formula>'קבוצות'!$E$3="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="18" dxfId="12">
-      <formula>'קבוצות'!$D$3="ירוק"</formula>
+      <formula>'קבוצות'!$E$3="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:F28">
     <cfRule type="expression" priority="19" dxfId="1">
-      <formula>'קבוצות'!$D$4="ורוד"</formula>
+      <formula>'קבוצות'!$E$4="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="22" dxfId="2">
-      <formula>'קבוצות'!$D$4="ים"</formula>
+      <formula>'קבוצות'!$E$4="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="25" dxfId="3">
-      <formula>'קבוצות'!$D$4="ספארי"</formula>
+      <formula>'קבוצות'!$E$4="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="28" dxfId="4">
-      <formula>'קבוצות'!$D$4="שדה"</formula>
+      <formula>'קבוצות'!$E$4="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="31" dxfId="5">
-      <formula>'קבוצות'!$D$4="סגול"</formula>
+      <formula>'קבוצות'!$E$4="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="34" dxfId="6">
-      <formula>'קבוצות'!$D$4="ירוק"</formula>
+      <formula>'קבוצות'!$E$4="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:A47">
     <cfRule type="expression" priority="20" dxfId="1">
-      <formula>'קבוצות'!$D$4="ורוד"</formula>
+      <formula>'קבוצות'!$E$4="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="23" dxfId="2">
-      <formula>'קבוצות'!$D$4="ים"</formula>
+      <formula>'קבוצות'!$E$4="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="26" dxfId="3">
-      <formula>'קבוצות'!$D$4="ספארי"</formula>
+      <formula>'קבוצות'!$E$4="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="29" dxfId="4">
-      <formula>'קבוצות'!$D$4="שדה"</formula>
+      <formula>'קבוצות'!$E$4="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="32" dxfId="5">
-      <formula>'קבוצות'!$D$4="סגול"</formula>
+      <formula>'קבוצות'!$E$4="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="35" dxfId="6">
-      <formula>'קבוצות'!$D$4="ירוק"</formula>
+      <formula>'קבוצות'!$E$4="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:F26">
     <cfRule type="expression" priority="21" dxfId="7">
-      <formula>'קבוצות'!$D$4="ורוד"</formula>
+      <formula>'קבוצות'!$E$4="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="24" dxfId="8">
-      <formula>'קבוצות'!$D$4="ים"</formula>
+      <formula>'קבוצות'!$E$4="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="27" dxfId="9">
-      <formula>'קבוצות'!$D$4="ספארי"</formula>
+      <formula>'קבוצות'!$E$4="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="30" dxfId="10">
-      <formula>'קבוצות'!$D$4="שדה"</formula>
+      <formula>'קבוצות'!$E$4="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="33" dxfId="11">
-      <formula>'קבוצות'!$D$4="סגול"</formula>
+      <formula>'קבוצות'!$E$4="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="36" dxfId="12">
-      <formula>'קבוצות'!$D$4="ירוק"</formula>
+      <formula>'קבוצות'!$E$4="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:F53">
     <cfRule type="expression" priority="37" dxfId="1">
-      <formula>'קבוצות'!$D$5="ורוד"</formula>
+      <formula>'קבוצות'!$E$5="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="40" dxfId="2">
-      <formula>'קבוצות'!$D$5="ים"</formula>
+      <formula>'קבוצות'!$E$5="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="43" dxfId="3">
-      <formula>'קבוצות'!$D$5="ספארי"</formula>
+      <formula>'קבוצות'!$E$5="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="46" dxfId="4">
-      <formula>'קבוצות'!$D$5="שדה"</formula>
+      <formula>'קבוצות'!$E$5="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="49" dxfId="5">
-      <formula>'קבוצות'!$D$5="סגול"</formula>
+      <formula>'קבוצות'!$E$5="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="52" dxfId="6">
-      <formula>'קבוצות'!$D$5="ירוק"</formula>
+      <formula>'קבוצות'!$E$5="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:A72">
     <cfRule type="expression" priority="38" dxfId="1">
-      <formula>'קבוצות'!$D$5="ורוד"</formula>
+      <formula>'קבוצות'!$E$5="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="41" dxfId="2">
-      <formula>'קבוצות'!$D$5="ים"</formula>
+      <formula>'קבוצות'!$E$5="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="44" dxfId="3">
-      <formula>'קבוצות'!$D$5="ספארי"</formula>
+      <formula>'קבוצות'!$E$5="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="47" dxfId="4">
-      <formula>'קבוצות'!$D$5="שדה"</formula>
+      <formula>'קבוצות'!$E$5="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="50" dxfId="5">
-      <formula>'קבוצות'!$D$5="סגול"</formula>
+      <formula>'קבוצות'!$E$5="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="53" dxfId="6">
-      <formula>'קבוצות'!$D$5="ירוק"</formula>
+      <formula>'קבוצות'!$E$5="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:F51">
     <cfRule type="expression" priority="39" dxfId="7">
-      <formula>'קבוצות'!$D$5="ורוד"</formula>
+      <formula>'קבוצות'!$E$5="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="42" dxfId="8">
-      <formula>'קבוצות'!$D$5="ים"</formula>
+      <formula>'קבוצות'!$E$5="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="45" dxfId="9">
-      <formula>'קבוצות'!$D$5="ספארי"</formula>
+      <formula>'קבוצות'!$E$5="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="48" dxfId="10">
-      <formula>'קבוצות'!$D$5="שדה"</formula>
+      <formula>'קבוצות'!$E$5="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="51" dxfId="11">
-      <formula>'קבוצות'!$D$5="סגול"</formula>
+      <formula>'קבוצות'!$E$5="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="54" dxfId="12">
-      <formula>'קבוצות'!$D$5="ירוק"</formula>
+      <formula>'קבוצות'!$E$5="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A77:F78">
     <cfRule type="expression" priority="55" dxfId="1">
-      <formula>'קבוצות'!$D$6="ורוד"</formula>
+      <formula>'קבוצות'!$E$6="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="58" dxfId="2">
-      <formula>'קבוצות'!$D$6="ים"</formula>
+      <formula>'קבוצות'!$E$6="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="61" dxfId="3">
-      <formula>'קבוצות'!$D$6="ספארי"</formula>
+      <formula>'קבוצות'!$E$6="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="64" dxfId="4">
-      <formula>'קבוצות'!$D$6="שדה"</formula>
+      <formula>'קבוצות'!$E$6="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="67" dxfId="5">
-      <formula>'קבוצות'!$D$6="סגול"</formula>
+      <formula>'קבוצות'!$E$6="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="70" dxfId="6">
-      <formula>'קבוצות'!$D$6="ירוק"</formula>
+      <formula>'קבוצות'!$E$6="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80:A97">
     <cfRule type="expression" priority="56" dxfId="1">
-      <formula>'קבוצות'!$D$6="ורוד"</formula>
+      <formula>'קבוצות'!$E$6="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="59" dxfId="2">
-      <formula>'קבוצות'!$D$6="ים"</formula>
+      <formula>'קבוצות'!$E$6="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="62" dxfId="3">
-      <formula>'קבוצות'!$D$6="ספארי"</formula>
+      <formula>'קבוצות'!$E$6="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="65" dxfId="4">
-      <formula>'קבוצות'!$D$6="שדה"</formula>
+      <formula>'קבוצות'!$E$6="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="68" dxfId="5">
-      <formula>'קבוצות'!$D$6="סגול"</formula>
+      <formula>'קבוצות'!$E$6="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="71" dxfId="6">
-      <formula>'קבוצות'!$D$6="ירוק"</formula>
+      <formula>'קבוצות'!$E$6="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:F76">
     <cfRule type="expression" priority="57" dxfId="7">
-      <formula>'קבוצות'!$D$6="ורוד"</formula>
+      <formula>'קבוצות'!$E$6="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="60" dxfId="8">
-      <formula>'קבוצות'!$D$6="ים"</formula>
+      <formula>'קבוצות'!$E$6="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="63" dxfId="9">
-      <formula>'קבוצות'!$D$6="ספארי"</formula>
+      <formula>'קבוצות'!$E$6="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="66" dxfId="10">
-      <formula>'קבוצות'!$D$6="שדה"</formula>
+      <formula>'קבוצות'!$E$6="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="69" dxfId="11">
-      <formula>'קבוצות'!$D$6="סגול"</formula>
+      <formula>'קבוצות'!$E$6="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="72" dxfId="12">
-      <formula>'קבוצות'!$D$6="ירוק"</formula>
+      <formula>'קבוצות'!$E$6="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102:F103">
     <cfRule type="expression" priority="73" dxfId="1">
-      <formula>'קבוצות'!$D$7="ורוד"</formula>
+      <formula>'קבוצות'!$E$7="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="76" dxfId="2">
-      <formula>'קבוצות'!$D$7="ים"</formula>
+      <formula>'קבוצות'!$E$7="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="79" dxfId="3">
-      <formula>'קבוצות'!$D$7="ספארי"</formula>
+      <formula>'קבוצות'!$E$7="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="82" dxfId="4">
-      <formula>'קבוצות'!$D$7="שדה"</formula>
+      <formula>'קבוצות'!$E$7="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="85" dxfId="5">
-      <formula>'קבוצות'!$D$7="סגול"</formula>
+      <formula>'קבוצות'!$E$7="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="88" dxfId="6">
-      <formula>'קבוצות'!$D$7="ירוק"</formula>
+      <formula>'קבוצות'!$E$7="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105:A122">
     <cfRule type="expression" priority="74" dxfId="1">
-      <formula>'קבוצות'!$D$7="ורוד"</formula>
+      <formula>'קבוצות'!$E$7="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="77" dxfId="2">
-      <formula>'קבוצות'!$D$7="ים"</formula>
+      <formula>'קבוצות'!$E$7="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="80" dxfId="3">
-      <formula>'קבוצות'!$D$7="ספארי"</formula>
+      <formula>'קבוצות'!$E$7="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="83" dxfId="4">
-      <formula>'קבוצות'!$D$7="שדה"</formula>
+      <formula>'קבוצות'!$E$7="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="86" dxfId="5">
-      <formula>'קבוצות'!$D$7="סגול"</formula>
+      <formula>'קבוצות'!$E$7="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="89" dxfId="6">
-      <formula>'קבוצות'!$D$7="ירוק"</formula>
+      <formula>'קבוצות'!$E$7="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A101:F101">
     <cfRule type="expression" priority="75" dxfId="7">
-      <formula>'קבוצות'!$D$7="ורוד"</formula>
+      <formula>'קבוצות'!$E$7="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="78" dxfId="8">
-      <formula>'קבוצות'!$D$7="ים"</formula>
+      <formula>'קבוצות'!$E$7="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="81" dxfId="9">
-      <formula>'קבוצות'!$D$7="ספארי"</formula>
+      <formula>'קבוצות'!$E$7="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="84" dxfId="10">
-      <formula>'קבוצות'!$D$7="שדה"</formula>
+      <formula>'קבוצות'!$E$7="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="87" dxfId="11">
-      <formula>'קבוצות'!$D$7="סגול"</formula>
+      <formula>'קבוצות'!$E$7="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="90" dxfId="12">
-      <formula>'קבוצות'!$D$7="ירוק"</formula>
+      <formula>'קבוצות'!$E$7="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A127:F128">
     <cfRule type="expression" priority="91" dxfId="1">
-      <formula>'קבוצות'!$D$8="ורוד"</formula>
+      <formula>'קבוצות'!$E$8="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="94" dxfId="2">
-      <formula>'קבוצות'!$D$8="ים"</formula>
+      <formula>'קבוצות'!$E$8="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="97" dxfId="3">
-      <formula>'קבוצות'!$D$8="ספארי"</formula>
+      <formula>'קבוצות'!$E$8="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="100" dxfId="4">
-      <formula>'קבוצות'!$D$8="שדה"</formula>
+      <formula>'קבוצות'!$E$8="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="103" dxfId="5">
-      <formula>'קבוצות'!$D$8="סגול"</formula>
+      <formula>'קבוצות'!$E$8="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="106" dxfId="6">
-      <formula>'קבוצות'!$D$8="ירוק"</formula>
+      <formula>'קבוצות'!$E$8="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A130:A147">
     <cfRule type="expression" priority="92" dxfId="1">
-      <formula>'קבוצות'!$D$8="ורוד"</formula>
+      <formula>'קבוצות'!$E$8="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="95" dxfId="2">
-      <formula>'קבוצות'!$D$8="ים"</formula>
+      <formula>'קבוצות'!$E$8="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="98" dxfId="3">
-      <formula>'קבוצות'!$D$8="ספארי"</formula>
+      <formula>'קבוצות'!$E$8="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="101" dxfId="4">
-      <formula>'קבוצות'!$D$8="שדה"</formula>
+      <formula>'קבוצות'!$E$8="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="104" dxfId="5">
-      <formula>'קבוצות'!$D$8="סגול"</formula>
+      <formula>'קבוצות'!$E$8="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="107" dxfId="6">
-      <formula>'קבוצות'!$D$8="ירוק"</formula>
+      <formula>'קבוצות'!$E$8="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A126:F126">
     <cfRule type="expression" priority="93" dxfId="7">
-      <formula>'קבוצות'!$D$8="ורוד"</formula>
+      <formula>'קבוצות'!$E$8="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="96" dxfId="8">
-      <formula>'קבוצות'!$D$8="ים"</formula>
+      <formula>'קבוצות'!$E$8="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="99" dxfId="9">
-      <formula>'קבוצות'!$D$8="ספארי"</formula>
+      <formula>'קבוצות'!$E$8="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="102" dxfId="10">
-      <formula>'קבוצות'!$D$8="שדה"</formula>
+      <formula>'קבוצות'!$E$8="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="105" dxfId="11">
-      <formula>'קבוצות'!$D$8="סגול"</formula>
+      <formula>'קבוצות'!$E$8="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="108" dxfId="12">
-      <formula>'קבוצות'!$D$8="ירוק"</formula>
+      <formula>'קבוצות'!$E$8="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/shabbatot/2026-09-04.xlsx
+++ b/shabbatot/2026-09-04.xlsx
@@ -400,7 +400,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
@@ -660,6 +660,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
@@ -1615,7 +1618,9 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C3" s="82" t="n"/>
+      <c r="C3" s="82" t="n">
+        <v>0.4375</v>
+      </c>
       <c r="D3" s="70" t="inlineStr">
         <is>
           <t>הכנת ארוחת צהריים שישי וניקיון אחריה</t>
@@ -1656,7 +1661,7 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="B4" s="69" t="inlineStr">
@@ -1664,10 +1669,12 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C4" s="82" t="n"/>
+      <c r="C4" s="82" t="n">
+        <v>0.5833333333333334</v>
+      </c>
       <c r="D4" s="70" t="inlineStr">
         <is>
-          <t>הכנסת אוכל מהקייטרינג לתנור חימום — כשעתיים לפני הקידוש</t>
+          <t>פריקת האוכל שמגיע מהקייטרינג</t>
         </is>
       </c>
       <c r="E4" s="83">
@@ -1705,7 +1712,7 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="B5" s="69" t="inlineStr">
@@ -1713,10 +1720,12 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C5" s="82" t="n"/>
+      <c r="C5" s="82" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="D5" s="70" t="inlineStr">
         <is>
-          <t>הוצאת האוכל מהתנור אחרי הקידוש ולפני הסעודה</t>
+          <t>הנחת האוכל על הפלטות, וחיבור מיחמים בפינת קפה</t>
         </is>
       </c>
       <c r="E5" s="83">
@@ -1754,7 +1763,7 @@
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="B6" s="69" t="inlineStr">
@@ -1762,10 +1771,12 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C6" s="82" t="n"/>
+      <c r="C6" s="82" t="n">
+        <v>0.8125</v>
+      </c>
       <c r="D6" s="70" t="inlineStr">
         <is>
-          <t>ארגון סלטים והכנת טחינה לשולחנות</t>
+          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
         </is>
       </c>
       <c r="E6" s="83">
@@ -1803,7 +1814,7 @@
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="B7" s="69" t="inlineStr">
@@ -1811,10 +1822,12 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C7" s="82" t="n"/>
+      <c r="C7" s="82" t="n">
+        <v>0.8125</v>
+      </c>
       <c r="D7" s="70" t="inlineStr">
         <is>
-          <t>עריכת שולחנות — כפות הגשה וחלוקת סלטים</t>
+          <t>עריכת שולחן — טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
         </is>
       </c>
       <c r="E7" s="83">
@@ -1852,7 +1865,7 @@
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="B8" s="69" t="inlineStr">
@@ -1860,10 +1873,12 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C8" s="82" t="n"/>
+      <c r="C8" s="82" t="n">
+        <v>0.875</v>
+      </c>
       <c r="D8" s="70" t="inlineStr">
         <is>
-          <t>ניקיון מרחב האוכל אחרי הסעודה</t>
+          <t>חימום 10 עוגות פרווה על הפלטה</t>
         </is>
       </c>
       <c r="E8" s="83">
@@ -1873,7 +1888,7 @@
       <c r="F8" s="70" t="n"/>
       <c r="G8" s="69" t="inlineStr">
         <is>
-          <t>סעודת שבת</t>
+          <t>טיש עם איש צוות</t>
         </is>
       </c>
       <c r="H8" s="84">
@@ -1901,7 +1916,7 @@
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="B9" s="69" t="inlineStr">
@@ -1909,10 +1924,12 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C9" s="82" t="n"/>
+      <c r="C9" s="82" t="n">
+        <v>0.875</v>
+      </c>
       <c r="D9" s="70" t="inlineStr">
         <is>
-          <t>הפיכת בית מיכאל לבית כנסת — מחיצה, שורות כיסאות משני הצדדים, סידורים על הכיסאות, הפעלת מזגן</t>
+          <t>חיתוך אבטיח</t>
         </is>
       </c>
       <c r="E9" s="83">
@@ -1922,7 +1939,7 @@
       <c r="F9" s="70" t="n"/>
       <c r="G9" s="69" t="inlineStr">
         <is>
-          <t>קבלת שבת וערבית</t>
+          <t>טיש עם איש צוות</t>
         </is>
       </c>
       <c r="H9" s="84">
@@ -1950,7 +1967,7 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="B10" s="69" t="inlineStr">
@@ -1958,10 +1975,12 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C10" s="82" t="n"/>
+      <c r="C10" s="82" t="n">
+        <v>0.8958333333333334</v>
+      </c>
       <c r="D10" s="70" t="inlineStr">
         <is>
-          <t>הבאת ספות וסידור מרחב הטיש</t>
+          <t>פריסת שולחן במרכז — 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
         </is>
       </c>
       <c r="E10" s="83">
@@ -1999,7 +2018,7 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · טיש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="B11" s="69" t="inlineStr">
@@ -2007,10 +2026,12 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C11" s="82" t="n"/>
+      <c r="C11" s="82" t="n">
+        <v>0.8958333333333334</v>
+      </c>
       <c r="D11" s="70" t="inlineStr">
         <is>
-          <t>סידור שולחנות וכיסאות לטיש</t>
+          <t>סידור המרחב בחדר האוכל — שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
         </is>
       </c>
       <c r="E11" s="83">
@@ -2048,7 +2069,7 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · טיש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="B12" s="69" t="inlineStr">
@@ -2059,7 +2080,7 @@
       <c r="C12" s="82" t="n"/>
       <c r="D12" s="70" t="inlineStr">
         <is>
-          <t>הבאת שתייה וסידור כוסות</t>
+          <t>ניקיון חדר האוכל בסיום הטיש — טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
         </is>
       </c>
       <c r="E12" s="83">
@@ -2097,18 +2118,20 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · טיש</t>
+          <t>בית מדרש · קידוש</t>
         </is>
       </c>
       <c r="B13" s="69" t="inlineStr">
         <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="C13" s="82" t="n"/>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C13" s="82" t="n">
+        <v>0.4375</v>
+      </c>
       <c r="D13" s="70" t="inlineStr">
         <is>
-          <t>חימום עוגות פרווה והוצאת כיבוד</t>
+          <t>סידור וניקיון פינת קפה — להוציא חלב, למלא קפה וסוכר</t>
         </is>
       </c>
       <c r="E13" s="83">
@@ -2118,7 +2141,7 @@
       <c r="F13" s="70" t="n"/>
       <c r="G13" s="69" t="inlineStr">
         <is>
-          <t>טיש עם איש צוות</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="H13" s="84">
@@ -2146,18 +2169,20 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · טיש</t>
+          <t>בית מדרש · קידוש</t>
         </is>
       </c>
       <c r="B14" s="69" t="inlineStr">
         <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="C14" s="82" t="n"/>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C14" s="82" t="n">
+        <v>0.4375</v>
+      </c>
       <c r="D14" s="70" t="inlineStr">
         <is>
-          <t>ניקיון מלא בסיום הטיש</t>
+          <t>חימום עוגות</t>
         </is>
       </c>
       <c r="E14" s="83">
@@ -2167,7 +2192,7 @@
       <c r="F14" s="70" t="n"/>
       <c r="G14" s="69" t="inlineStr">
         <is>
-          <t>טיש עם איש צוות</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="H14" s="84">
@@ -2195,18 +2220,20 @@
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · טיש</t>
+          <t>בית מדרש · קידוש</t>
         </is>
       </c>
       <c r="B15" s="69" t="inlineStr">
         <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
-      <c r="C15" s="82" t="n"/>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C15" s="82" t="n">
+        <v>0.4375</v>
+      </c>
       <c r="D15" s="70" t="inlineStr">
         <is>
-          <t>טאטוא ושטיפת בית מיכאל</t>
+          <t>טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
         </is>
       </c>
       <c r="E15" s="83">
@@ -2216,7 +2243,7 @@
       <c r="F15" s="70" t="n"/>
       <c r="G15" s="69" t="inlineStr">
         <is>
-          <t>ניקיונות וארגון הקמפוס</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="H15" s="84">
@@ -2244,18 +2271,20 @@
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · טיש</t>
+          <t>בית מדרש · קידוש</t>
         </is>
       </c>
       <c r="B16" s="69" t="inlineStr">
         <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
-      <c r="C16" s="82" t="n"/>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C16" s="82" t="n">
+        <v>0.4375</v>
+      </c>
       <c r="D16" s="70" t="inlineStr">
         <is>
-          <t>החזרת בית המדרש לסידור המקורי</t>
+          <t>הוצאת 15 עוגות, חלב, קורנפלקס, ענבים ואבטיח</t>
         </is>
       </c>
       <c r="E16" s="83">
@@ -2265,7 +2294,7 @@
       <c r="F16" s="70" t="n"/>
       <c r="G16" s="69" t="inlineStr">
         <is>
-          <t>ניקיונות וארגון הקמפוס</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="H16" s="84">
@@ -2301,10 +2330,12 @@
           <t>שבת</t>
         </is>
       </c>
-      <c r="C17" s="82" t="n"/>
+      <c r="C17" s="82" t="n">
+        <v>0.4375</v>
+      </c>
       <c r="D17" s="70" t="inlineStr">
         <is>
-          <t>חימום האוכל הרלוונטי בלבד לקידוש על הפלטות</t>
+          <t>חיתוך האבטיח</t>
         </is>
       </c>
       <c r="E17" s="83">
@@ -2342,7 +2373,7 @@
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · צהריים בשבת</t>
         </is>
       </c>
       <c r="B18" s="69" t="inlineStr">
@@ -2350,10 +2381,12 @@
           <t>שבת</t>
         </is>
       </c>
-      <c r="C18" s="82" t="n"/>
+      <c r="C18" s="82" t="n">
+        <v>0.4583333333333333</v>
+      </c>
       <c r="D18" s="70" t="inlineStr">
         <is>
-          <t>הכנסת מאפים לתנור חימום — ללא אלומיניום מעל העוגות</t>
+          <t>הנחת האוכל בתנור החימום</t>
         </is>
       </c>
       <c r="E18" s="83">
@@ -2363,7 +2396,7 @@
       <c r="F18" s="70" t="n"/>
       <c r="G18" s="69" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="H18" s="84">
@@ -2391,7 +2424,7 @@
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · צהריים בשבת</t>
         </is>
       </c>
       <c r="B19" s="69" t="inlineStr">
@@ -2399,10 +2432,12 @@
           <t>שבת</t>
         </is>
       </c>
-      <c r="C19" s="82" t="n"/>
+      <c r="C19" s="82" t="n">
+        <v>0.5208333333333334</v>
+      </c>
       <c r="D19" s="70" t="inlineStr">
         <is>
-          <t>תיבול סלטים לקידוש</t>
+          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם</t>
         </is>
       </c>
       <c r="E19" s="83">
@@ -2412,7 +2447,7 @@
       <c r="F19" s="70" t="n"/>
       <c r="G19" s="69" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="H19" s="84">
@@ -2440,7 +2475,7 @@
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · צהריים בשבת</t>
         </is>
       </c>
       <c r="B20" s="69" t="inlineStr">
@@ -2448,10 +2483,12 @@
           <t>שבת</t>
         </is>
       </c>
-      <c r="C20" s="82" t="n"/>
+      <c r="C20" s="82" t="n">
+        <v>0.5208333333333334</v>
+      </c>
       <c r="D20" s="70" t="inlineStr">
         <is>
-          <t>עריכת האוכל לקידוש</t>
+          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
         </is>
       </c>
       <c r="E20" s="83">
@@ -2461,7 +2498,7 @@
       <c r="F20" s="70" t="n"/>
       <c r="G20" s="69" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="H20" s="84">
@@ -2487,32 +2524,16 @@
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="80" t="inlineStr">
-        <is>
-          <t>בית מדרש · קידוש</t>
-        </is>
-      </c>
-      <c r="B21" s="69" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
+      <c r="A21" s="80" t="n"/>
+      <c r="B21" s="69" t="n"/>
       <c r="C21" s="82" t="n"/>
-      <c r="D21" s="70" t="inlineStr">
-        <is>
-          <t>סידור פינת קפה — ניקוי, חלב, קפה וסוכר</t>
-        </is>
-      </c>
+      <c r="D21" s="70" t="n"/>
       <c r="E21" s="83">
         <f>IF($D21="","",IFERROR(INDEX('מאגר משימות'!$A$3:$A$252,MATCH($D21,'מאגר משימות'!$D$3:$D$252,0)),""))</f>
         <v/>
       </c>
       <c r="F21" s="70" t="n"/>
-      <c r="G21" s="69" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
+      <c r="G21" s="69" t="n"/>
       <c r="H21" s="84">
         <f>IF($D21="","",IF($C21="","",TEXT(HOUR($C21),"00")&amp;":"&amp;TEXT(MINUTE($C21),"00")&amp;" · ")&amp;$D21&amp;IF($A21="",""," — "&amp;$A21)&amp;IF($F21="",""," ("&amp;$F21&amp;")"))</f>
         <v/>
@@ -2536,32 +2557,16 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="80" t="inlineStr">
-        <is>
-          <t>בית מדרש · קידוש</t>
-        </is>
-      </c>
-      <c r="B22" s="69" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
+      <c r="A22" s="80" t="n"/>
+      <c r="B22" s="69" t="n"/>
       <c r="C22" s="82" t="n"/>
-      <c r="D22" s="70" t="inlineStr">
-        <is>
-          <t>הוצאת פירות חתוכים ועוגות</t>
-        </is>
-      </c>
+      <c r="D22" s="70" t="n"/>
       <c r="E22" s="83">
         <f>IF($D22="","",IFERROR(INDEX('מאגר משימות'!$A$3:$A$252,MATCH($D22,'מאגר משימות'!$D$3:$D$252,0)),""))</f>
         <v/>
       </c>
       <c r="F22" s="70" t="n"/>
-      <c r="G22" s="69" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
+      <c r="G22" s="69" t="n"/>
       <c r="H22" s="84">
         <f>IF($D22="","",IF($C22="","",TEXT(HOUR($C22),"00")&amp;":"&amp;TEXT(MINUTE($C22),"00")&amp;" · ")&amp;$D22&amp;IF($A22="",""," — "&amp;$A22)&amp;IF($F22="",""," ("&amp;$F22&amp;")"))</f>
         <v/>
@@ -2585,32 +2590,16 @@
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="80" t="inlineStr">
-        <is>
-          <t>בית מדרש · קידוש</t>
-        </is>
-      </c>
-      <c r="B23" s="69" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
+      <c r="A23" s="80" t="n"/>
+      <c r="B23" s="69" t="n"/>
       <c r="C23" s="82" t="n"/>
-      <c r="D23" s="70" t="inlineStr">
-        <is>
-          <t>הוצאת כלים וסידור שולחנות במעגל</t>
-        </is>
-      </c>
+      <c r="D23" s="70" t="n"/>
       <c r="E23" s="83">
         <f>IF($D23="","",IFERROR(INDEX('מאגר משימות'!$A$3:$A$252,MATCH($D23,'מאגר משימות'!$D$3:$D$252,0)),""))</f>
         <v/>
       </c>
       <c r="F23" s="70" t="n"/>
-      <c r="G23" s="69" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
+      <c r="G23" s="69" t="n"/>
       <c r="H23" s="84">
         <f>IF($D23="","",IF($C23="","",TEXT(HOUR($C23),"00")&amp;":"&amp;TEXT(MINUTE($C23),"00")&amp;" · ")&amp;$D23&amp;IF($A23="",""," — "&amp;$A23)&amp;IF($F23="",""," ("&amp;$F23&amp;")"))</f>
         <v/>
@@ -2634,32 +2623,16 @@
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="80" t="inlineStr">
-        <is>
-          <t>בית מדרש · קידוש</t>
-        </is>
-      </c>
-      <c r="B24" s="69" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
+      <c r="A24" s="80" t="n"/>
+      <c r="B24" s="69" t="n"/>
       <c r="C24" s="82" t="n"/>
-      <c r="D24" s="70" t="inlineStr">
-        <is>
-          <t>ניקיון מרחב האוכל אחרי הקידוש</t>
-        </is>
-      </c>
+      <c r="D24" s="70" t="n"/>
       <c r="E24" s="83">
         <f>IF($D24="","",IFERROR(INDEX('מאגר משימות'!$A$3:$A$252,MATCH($D24,'מאגר משימות'!$D$3:$D$252,0)),""))</f>
         <v/>
       </c>
       <c r="F24" s="70" t="n"/>
-      <c r="G24" s="69" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
+      <c r="G24" s="69" t="n"/>
       <c r="H24" s="84">
         <f>IF($D24="","",IF($C24="","",TEXT(HOUR($C24),"00")&amp;":"&amp;TEXT(MINUTE($C24),"00")&amp;" · ")&amp;$D24&amp;IF($A24="",""," — "&amp;$A24)&amp;IF($F24="",""," ("&amp;$F24&amp;")"))</f>
         <v/>
@@ -2683,32 +2656,16 @@
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="80" t="inlineStr">
-        <is>
-          <t>בית מדרש · קידוש</t>
-        </is>
-      </c>
-      <c r="B25" s="69" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
+      <c r="A25" s="80" t="n"/>
+      <c r="B25" s="69" t="n"/>
       <c r="C25" s="82" t="n"/>
-      <c r="D25" s="70" t="inlineStr">
-        <is>
-          <t>קיפול והכנסה למקרר בסיום — לא להשאיר אוכל פתוח</t>
-        </is>
-      </c>
+      <c r="D25" s="70" t="n"/>
       <c r="E25" s="83">
         <f>IF($D25="","",IFERROR(INDEX('מאגר משימות'!$A$3:$A$252,MATCH($D25,'מאגר משימות'!$D$3:$D$252,0)),""))</f>
         <v/>
       </c>
       <c r="F25" s="70" t="n"/>
-      <c r="G25" s="69" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
+      <c r="G25" s="69" t="n"/>
       <c r="H25" s="84">
         <f>IF($D25="","",IF($C25="","",TEXT(HOUR($C25),"00")&amp;":"&amp;TEXT(MINUTE($C25),"00")&amp;" · ")&amp;$D25&amp;IF($A25="",""," — "&amp;$A25)&amp;IF($F25="",""," ("&amp;$F25&amp;")"))</f>
         <v/>
@@ -2732,32 +2689,16 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="80" t="inlineStr">
-        <is>
-          <t>בית מדרש · צהריים בשבת</t>
-        </is>
-      </c>
-      <c r="B26" s="69" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
+      <c r="A26" s="80" t="n"/>
+      <c r="B26" s="69" t="n"/>
       <c r="C26" s="82" t="n"/>
-      <c r="D26" s="70" t="inlineStr">
-        <is>
-          <t>הכנסת אוכל מהקייטרינג לתנור חימום — כשעתיים לפני ארוחת הצהריים</t>
-        </is>
-      </c>
+      <c r="D26" s="70" t="n"/>
       <c r="E26" s="83">
         <f>IF($D26="","",IFERROR(INDEX('מאגר משימות'!$A$3:$A$252,MATCH($D26,'מאגר משימות'!$D$3:$D$252,0)),""))</f>
         <v/>
       </c>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="69" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
+      <c r="G26" s="69" t="n"/>
       <c r="H26" s="84">
         <f>IF($D26="","",IF($C26="","",TEXT(HOUR($C26),"00")&amp;":"&amp;TEXT(MINUTE($C26),"00")&amp;" · ")&amp;$D26&amp;IF($A26="",""," — "&amp;$A26)&amp;IF($F26="",""," ("&amp;$F26&amp;")"))</f>
         <v/>
@@ -2781,32 +2722,16 @@
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="80" t="inlineStr">
-        <is>
-          <t>בית מדרש · צהריים בשבת</t>
-        </is>
-      </c>
-      <c r="B27" s="69" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
+      <c r="A27" s="80" t="n"/>
+      <c r="B27" s="69" t="n"/>
       <c r="C27" s="82" t="n"/>
-      <c r="D27" s="70" t="inlineStr">
-        <is>
-          <t>עריכת שולחן לארוחת צהריים אחרי הקידוש</t>
-        </is>
-      </c>
+      <c r="D27" s="70" t="n"/>
       <c r="E27" s="83">
         <f>IF($D27="","",IFERROR(INDEX('מאגר משימות'!$A$3:$A$252,MATCH($D27,'מאגר משימות'!$D$3:$D$252,0)),""))</f>
         <v/>
       </c>
       <c r="F27" s="70" t="n"/>
-      <c r="G27" s="69" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
+      <c r="G27" s="69" t="n"/>
       <c r="H27" s="84">
         <f>IF($D27="","",IF($C27="","",TEXT(HOUR($C27),"00")&amp;":"&amp;TEXT(MINUTE($C27),"00")&amp;" · ")&amp;$D27&amp;IF($A27="",""," — "&amp;$A27)&amp;IF($F27="",""," ("&amp;$F27&amp;")"))</f>
         <v/>
@@ -2830,32 +2755,16 @@
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="80" t="inlineStr">
-        <is>
-          <t>בית מדרש · צהריים בשבת</t>
-        </is>
-      </c>
-      <c r="B28" s="69" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
+      <c r="A28" s="80" t="n"/>
+      <c r="B28" s="69" t="n"/>
       <c r="C28" s="82" t="n"/>
-      <c r="D28" s="70" t="inlineStr">
-        <is>
-          <t>חלוקת סלטים לשולחנות</t>
-        </is>
-      </c>
+      <c r="D28" s="70" t="n"/>
       <c r="E28" s="83">
         <f>IF($D28="","",IFERROR(INDEX('מאגר משימות'!$A$3:$A$252,MATCH($D28,'מאגר משימות'!$D$3:$D$252,0)),""))</f>
         <v/>
       </c>
       <c r="F28" s="70" t="n"/>
-      <c r="G28" s="69" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
+      <c r="G28" s="69" t="n"/>
       <c r="H28" s="84">
         <f>IF($D28="","",IF($C28="","",TEXT(HOUR($C28),"00")&amp;":"&amp;TEXT(MINUTE($C28),"00")&amp;" · ")&amp;$D28&amp;IF($A28="",""," — "&amp;$A28)&amp;IF($F28="",""," ("&amp;$F28&amp;")"))</f>
         <v/>
@@ -2879,32 +2788,16 @@
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="80" t="inlineStr">
-        <is>
-          <t>בית מדרש · צהריים בשבת</t>
-        </is>
-      </c>
-      <c r="B29" s="69" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
+      <c r="A29" s="80" t="n"/>
+      <c r="B29" s="69" t="n"/>
       <c r="C29" s="82" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
-        <is>
-          <t>ניקיון מרחב האוכל אחרי ארוחת הצהריים</t>
-        </is>
-      </c>
+      <c r="D29" s="70" t="n"/>
       <c r="E29" s="83">
         <f>IF($D29="","",IFERROR(INDEX('מאגר משימות'!$A$3:$A$252,MATCH($D29,'מאגר משימות'!$D$3:$D$252,0)),""))</f>
         <v/>
       </c>
       <c r="F29" s="70" t="n"/>
-      <c r="G29" s="69" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
+      <c r="G29" s="69" t="n"/>
       <c r="H29" s="84">
         <f>IF($D29="","",IF($C29="","",TEXT(HOUR($C29),"00")&amp;":"&amp;TEXT(MINUTE($C29),"00")&amp;" · ")&amp;$D29&amp;IF($A29="",""," — "&amp;$A29)&amp;IF($F29="",""," ("&amp;$F29&amp;")"))</f>
         <v/>
@@ -7454,7 +7347,7 @@
       </c>
       <c r="B3" s="69" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="C3" s="69" t="n"/>
@@ -7688,11 +7581,7 @@
           <t>יהב לוי</t>
         </is>
       </c>
-      <c r="B7" s="69" t="inlineStr">
-        <is>
-          <t>עוגות · צוות יותם</t>
-        </is>
-      </c>
+      <c r="B7" s="69" t="n"/>
       <c r="C7" s="69" t="n"/>
       <c r="D7" s="86" t="n"/>
       <c r="F7" s="85">
@@ -7752,7 +7641,7 @@
       </c>
       <c r="B8" s="69" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="C8" s="69" t="n"/>
@@ -8112,7 +8001,7 @@
       </c>
       <c r="B14" s="69" t="inlineStr">
         <is>
-          <t>בית מדרש · טיש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="C14" s="69" t="n"/>
@@ -8174,7 +8063,7 @@
       </c>
       <c r="B15" s="69" t="inlineStr">
         <is>
-          <t>בית מדרש · טיש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="C15" s="69" t="n"/>
@@ -8472,7 +8361,7 @@
       </c>
       <c r="B20" s="69" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="C20" s="69" t="n"/>
@@ -8590,7 +8479,11 @@
           <t>יואב אוחנה</t>
         </is>
       </c>
-      <c r="B22" s="69" t="n"/>
+      <c r="B22" s="69" t="inlineStr">
+        <is>
+          <t>עוגות · צוות יותם</t>
+        </is>
+      </c>
       <c r="C22" s="69" t="n"/>
       <c r="D22" s="86" t="n"/>
       <c r="F22" s="85">
@@ -8764,7 +8657,11 @@
           <t>הילה עזרא</t>
         </is>
       </c>
-      <c r="B25" s="69" t="n"/>
+      <c r="B25" s="69" t="inlineStr">
+        <is>
+          <t>עוגות · צוות רותם</t>
+        </is>
+      </c>
       <c r="C25" s="69" t="n"/>
       <c r="D25" s="86" t="n"/>
       <c r="F25" s="85">
@@ -9410,11 +9307,7 @@
           <t>שירה ספונוב</t>
         </is>
       </c>
-      <c r="B36" s="69" t="inlineStr">
-        <is>
-          <t>עוגות · צוות רותם</t>
-        </is>
-      </c>
+      <c r="B36" s="69" t="n"/>
       <c r="C36" s="69" t="n"/>
       <c r="D36" s="86" t="n"/>
       <c r="F36" s="85">
@@ -10306,7 +10199,7 @@
       </c>
       <c r="B51" s="69" t="inlineStr">
         <is>
-          <t>בית מדרש · טיש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="C51" s="69" t="n"/>
@@ -11840,11 +11733,7 @@
           <t>איתי גוסטינר</t>
         </is>
       </c>
-      <c r="B77" s="69" t="inlineStr">
-        <is>
-          <t>בית מדרש · טיש</t>
-        </is>
-      </c>
+      <c r="B77" s="69" t="n"/>
       <c r="C77" s="69" t="n"/>
       <c r="D77" s="86" t="n"/>
       <c r="F77" s="85">
@@ -12024,7 +11913,7 @@
       </c>
       <c r="B80" s="69" t="inlineStr">
         <is>
-          <t>בית מדרש · טיש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="C80" s="69" t="n"/>
@@ -12148,7 +12037,7 @@
       </c>
       <c r="B82" s="69" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="C82" s="69" t="n"/>
@@ -12392,7 +12281,7 @@
       </c>
       <c r="B86" s="69" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="C86" s="69" t="n"/>
@@ -12576,7 +12465,11 @@
           <t>עליזה בלום</t>
         </is>
       </c>
-      <c r="B89" s="69" t="n"/>
+      <c r="B89" s="69" t="inlineStr">
+        <is>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
+        </is>
+      </c>
       <c r="C89" s="69" t="n"/>
       <c r="D89" s="86" t="n"/>
       <c r="F89" s="85">
@@ -15206,7 +15099,7 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="B8" s="86" t="n"/>
@@ -15232,7 +15125,7 @@
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · טיש</t>
+          <t>בית מדרש · קידוש</t>
         </is>
       </c>
       <c r="B9" s="86" t="n"/>
@@ -15258,7 +15151,7 @@
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · צהריים בשבת</t>
         </is>
       </c>
       <c r="B10" s="86" t="n"/>
@@ -15282,26 +15175,14 @@
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="80" t="inlineStr">
-        <is>
-          <t>בית מדרש · צהריים בשבת</t>
-        </is>
-      </c>
+      <c r="A11" s="80" t="n"/>
       <c r="B11" s="86" t="n"/>
-      <c r="C11" s="69" t="inlineStr">
-        <is>
-          <t>בית מדרש ופינת קפה</t>
-        </is>
-      </c>
+      <c r="C11" s="69" t="n"/>
       <c r="D11" s="87">
         <f>IF($A11="","",'חניכים'!$N$132&amp;"")</f>
         <v/>
       </c>
-      <c r="E11" s="69" t="inlineStr">
-        <is>
-          <t>ים</t>
-        </is>
-      </c>
+      <c r="E11" s="69" t="n"/>
       <c r="F11" s="88">
         <f>IF($A11="","",COUNTIF('חניכים'!$B$3:$B$132,$A11))</f>
         <v/>
@@ -15375,14 +15256,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E254"/>
+  <dimension ref="A1:F254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -15415,6 +15297,11 @@
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
+          <t>שעה</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
           <t>עוגן בלו"ז</t>
         </is>
       </c>
@@ -15440,7 +15327,8 @@
           <t>הכנת בצקים לעוגות ולחלות</t>
         </is>
       </c>
-      <c r="E3" s="76" t="inlineStr">
+      <c r="E3" s="90" t="n"/>
+      <c r="F3" s="76" t="inlineStr">
         <is>
           <t>חמישי — הכנות</t>
         </is>
@@ -15467,7 +15355,8 @@
           <t>אפיית חלות</t>
         </is>
       </c>
-      <c r="E4" s="76" t="inlineStr">
+      <c r="E4" s="90" t="n"/>
+      <c r="F4" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15494,7 +15383,8 @@
           <t>אפיית לחמניות</t>
         </is>
       </c>
-      <c r="E5" s="76" t="inlineStr">
+      <c r="E5" s="90" t="n"/>
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15521,7 +15411,8 @@
           <t>בייגל בייטס</t>
         </is>
       </c>
-      <c r="E6" s="76" t="inlineStr">
+      <c r="E6" s="90" t="n"/>
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15548,7 +15439,8 @@
           <t>פנקייקים</t>
         </is>
       </c>
-      <c r="E7" s="76" t="inlineStr">
+      <c r="E7" s="90" t="n"/>
+      <c r="F7" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15575,7 +15467,8 @@
           <t>עוגות שמרים</t>
         </is>
       </c>
-      <c r="E8" s="76" t="inlineStr">
+      <c r="E8" s="90" t="n"/>
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15602,7 +15495,8 @@
           <t>עוגות בננה עם שוקו צ'יפס</t>
         </is>
       </c>
-      <c r="E9" s="76" t="inlineStr">
+      <c r="E9" s="90" t="n"/>
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15629,7 +15523,8 @@
           <t>עוגות גזר</t>
         </is>
       </c>
-      <c r="E10" s="76" t="inlineStr">
+      <c r="E10" s="90" t="n"/>
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15656,7 +15551,8 @@
           <t>עוגת ביסקוויטים גבינה</t>
         </is>
       </c>
-      <c r="E11" s="76" t="inlineStr">
+      <c r="E11" s="90" t="n"/>
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15683,7 +15579,8 @@
           <t>עוגיות שוקולד צ'יפס</t>
         </is>
       </c>
-      <c r="E12" s="76" t="inlineStr">
+      <c r="E12" s="90" t="n"/>
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15710,7 +15607,8 @@
           <t>כדורי שוקולד פרווה</t>
         </is>
       </c>
-      <c r="E13" s="76" t="inlineStr">
+      <c r="E13" s="90" t="n"/>
+      <c r="F13" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15734,10 +15632,11 @@
       </c>
       <c r="D14" s="68" t="inlineStr">
         <is>
-          <t>עוגות לסעודה שלישית</t>
-        </is>
-      </c>
-      <c r="E14" s="76" t="inlineStr">
+          <t>עוגות פרווה לטיש</t>
+        </is>
+      </c>
+      <c r="E14" s="90" t="n"/>
+      <c r="F14" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15751,7 +15650,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>בישול</t>
+          <t>מאפים</t>
         </is>
       </c>
       <c r="C15" s="76" t="inlineStr">
@@ -15761,10 +15660,11 @@
       </c>
       <c r="D15" s="68" t="inlineStr">
         <is>
-          <t>סלטים לארוחת ערב שבת</t>
-        </is>
-      </c>
-      <c r="E15" s="76" t="inlineStr">
+          <t>עוגות לסעודה שלישית</t>
+        </is>
+      </c>
+      <c r="E15" s="90" t="n"/>
+      <c r="F15" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15788,10 +15688,11 @@
       </c>
       <c r="D16" s="68" t="inlineStr">
         <is>
-          <t>סלטים לארוחת צהריים שבת</t>
-        </is>
-      </c>
-      <c r="E16" s="76" t="inlineStr">
+          <t>סלטים לארוחת ערב שבת</t>
+        </is>
+      </c>
+      <c r="E16" s="90" t="n"/>
+      <c r="F16" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15815,10 +15716,11 @@
       </c>
       <c r="D17" s="68" t="inlineStr">
         <is>
-          <t>סלט ביצים</t>
-        </is>
-      </c>
-      <c r="E17" s="76" t="inlineStr">
+          <t>סלטים לארוחת צהריים שבת</t>
+        </is>
+      </c>
+      <c r="E17" s="90" t="n"/>
+      <c r="F17" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15842,10 +15744,11 @@
       </c>
       <c r="D18" s="68" t="inlineStr">
         <is>
-          <t>מטבוחה</t>
-        </is>
-      </c>
-      <c r="E18" s="76" t="inlineStr">
+          <t>סלט ביצים</t>
+        </is>
+      </c>
+      <c r="E18" s="90" t="n"/>
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15869,10 +15772,11 @@
       </c>
       <c r="D19" s="68" t="inlineStr">
         <is>
-          <t>חיתוך ירקות לסלט</t>
-        </is>
-      </c>
-      <c r="E19" s="76" t="inlineStr">
+          <t>מטבוחה</t>
+        </is>
+      </c>
+      <c r="E19" s="90" t="n"/>
+      <c r="F19" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15891,2635 +15795,2804 @@
       </c>
       <c r="C20" s="76" t="inlineStr">
         <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D20" s="68" t="inlineStr">
+        <is>
+          <t>חיתוך ירקות לסלט</t>
+        </is>
+      </c>
+      <c r="E20" s="90" t="n"/>
+      <c r="F20" s="76" t="inlineStr">
+        <is>
+          <t>שישי — הכנות ועבודה</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת בוקר שישי</t>
+        </is>
+      </c>
+      <c r="C21" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D21" s="68" t="inlineStr">
+        <is>
+          <t>הכנת ארוחת בוקר שישי וניקיון אחריה</t>
+        </is>
+      </c>
+      <c r="E21" s="90" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="F21" s="76" t="inlineStr">
+        <is>
+          <t>שישי — ארוחת בוקר</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שישי</t>
+        </is>
+      </c>
+      <c r="C22" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D22" s="68" t="inlineStr">
+        <is>
+          <t>הכנת ארוחת צהריים שישי וניקיון אחריה</t>
+        </is>
+      </c>
+      <c r="E22" s="90" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F22" s="76" t="inlineStr">
+        <is>
+          <t>שישי — ארוחת צהריים</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת ערב שבת</t>
+        </is>
+      </c>
+      <c r="C23" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D23" s="68" t="inlineStr">
+        <is>
+          <t>פריקת האוכל שמגיע מהקייטרינג</t>
+        </is>
+      </c>
+      <c r="E23" s="90" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F23" s="76" t="inlineStr">
+        <is>
+          <t>סעודת שבת</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת ערב שבת</t>
+        </is>
+      </c>
+      <c r="C24" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D24" s="68" t="inlineStr">
+        <is>
+          <t>הנחת האוכל על הפלטות, וחיבור מיחמים בפינת קפה</t>
+        </is>
+      </c>
+      <c r="E24" s="90" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="F24" s="76" t="inlineStr">
+        <is>
+          <t>סעודת שבת</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת ערב שבת</t>
+        </is>
+      </c>
+      <c r="C25" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D25" s="68" t="inlineStr">
+        <is>
+          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
+        </is>
+      </c>
+      <c r="E25" s="90" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F25" s="76" t="inlineStr">
+        <is>
+          <t>סעודת שבת</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת ערב שבת</t>
+        </is>
+      </c>
+      <c r="C26" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D26" s="68" t="inlineStr">
+        <is>
+          <t>עריכת שולחן — טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
+        </is>
+      </c>
+      <c r="E26" s="90" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F26" s="76" t="inlineStr">
+        <is>
+          <t>סעודת שבת</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="C27" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D27" s="68" t="inlineStr">
+        <is>
+          <t>חימום 10 עוגות פרווה על הפלטה</t>
+        </is>
+      </c>
+      <c r="E27" s="90" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F27" s="76" t="inlineStr">
+        <is>
+          <t>טיש עם איש צוות</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="C28" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D28" s="68" t="inlineStr">
+        <is>
+          <t>חיתוך אבטיח</t>
+        </is>
+      </c>
+      <c r="E28" s="90" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F28" s="76" t="inlineStr">
+        <is>
+          <t>טיש עם איש צוות</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="C29" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D29" s="68" t="inlineStr">
+        <is>
+          <t>פריסת שולחן במרכז — 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
+        </is>
+      </c>
+      <c r="E29" s="90" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="F29" s="76" t="inlineStr">
+        <is>
+          <t>טיש עם איש צוות</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="C30" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D30" s="68" t="inlineStr">
+        <is>
+          <t>סידור המרחב בחדר האוכל — שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
+        </is>
+      </c>
+      <c r="E30" s="90" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="F30" s="76" t="inlineStr">
+        <is>
+          <t>טיש עם איש צוות</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="C31" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D31" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון חדר האוכל בסיום הטיש — טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+        </is>
+      </c>
+      <c r="E31" s="90" t="n"/>
+      <c r="F31" s="76" t="inlineStr">
+        <is>
+          <t>טיש עם איש צוות</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+      <c r="C32" s="76" t="inlineStr">
+        <is>
           <t>שבת</t>
         </is>
       </c>
-      <c r="D20" s="68" t="inlineStr">
-        <is>
-          <t>חיתוך פירות לקידוש</t>
-        </is>
-      </c>
-      <c r="E20" s="76" t="inlineStr">
+      <c r="D32" s="68" t="inlineStr">
+        <is>
+          <t>סידור וניקיון פינת קפה — להוציא חלב, למלא קפה וסוכר</t>
+        </is>
+      </c>
+      <c r="E32" s="90" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F32" s="76" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+      <c r="C33" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D33" s="68" t="inlineStr">
+        <is>
+          <t>חימום עוגות</t>
+        </is>
+      </c>
+      <c r="E33" s="90" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F33" s="76" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+      <c r="C34" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D34" s="68" t="inlineStr">
+        <is>
+          <t>טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
+        </is>
+      </c>
+      <c r="E34" s="90" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F34" s="76" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+      <c r="C35" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D35" s="68" t="inlineStr">
+        <is>
+          <t>הוצאת 15 עוגות, חלב, קורנפלקס, ענבים ואבטיח</t>
+        </is>
+      </c>
+      <c r="E35" s="90" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F35" s="76" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+      <c r="C36" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D36" s="68" t="inlineStr">
+        <is>
+          <t>חיתוך האבטיח</t>
+        </is>
+      </c>
+      <c r="E36" s="90" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F36" s="76" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שבת</t>
+        </is>
+      </c>
+      <c r="C37" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D37" s="68" t="inlineStr">
+        <is>
+          <t>הנחת האוכל בתנור החימום</t>
+        </is>
+      </c>
+      <c r="E37" s="90" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="F37" s="76" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שבת</t>
+        </is>
+      </c>
+      <c r="C38" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D38" s="68" t="inlineStr">
+        <is>
+          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם</t>
+        </is>
+      </c>
+      <c r="E38" s="90" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="F38" s="76" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שבת</t>
+        </is>
+      </c>
+      <c r="C39" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D39" s="68" t="inlineStr">
+        <is>
+          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+        </is>
+      </c>
+      <c r="E39" s="90" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="F39" s="76" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>סעודה שלישית</t>
+        </is>
+      </c>
+      <c r="C40" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D40" s="68" t="inlineStr">
+        <is>
+          <t>הכנסת מאפים לחימום והוצאת האוכל</t>
+        </is>
+      </c>
+      <c r="E40" s="90" t="n"/>
+      <c r="F40" s="76" t="inlineStr">
+        <is>
+          <t>סעודה שלישית</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>סעודה שלישית</t>
+        </is>
+      </c>
+      <c r="C41" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D41" s="68" t="inlineStr">
+        <is>
+          <t>עריכת המרחב וסידור בסיום</t>
+        </is>
+      </c>
+      <c r="E41" s="90" t="n"/>
+      <c r="F41" s="76" t="inlineStr">
+        <is>
+          <t>סעודה שלישית</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>בית מיכאל</t>
+        </is>
+      </c>
+      <c r="C42" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D42" s="68" t="inlineStr">
+        <is>
+          <t>הפיכת בית מיכאל לבית כנסת — מחיצה, שורות כיסאות משני הצדדים, סידורים על הכיסאות, הפעלת מזגן</t>
+        </is>
+      </c>
+      <c r="E42" s="90" t="n"/>
+      <c r="F42" s="76" t="inlineStr">
+        <is>
+          <t>קבלת שבת וערבית</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>בית מיכאל</t>
+        </is>
+      </c>
+      <c r="C43" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D43" s="68" t="inlineStr">
+        <is>
+          <t>הבאת ספות וסידור מרחב הטיש</t>
+        </is>
+      </c>
+      <c r="E43" s="90" t="n"/>
+      <c r="F43" s="76" t="inlineStr">
+        <is>
+          <t>טיש עם איש צוות</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>בית מיכאל</t>
+        </is>
+      </c>
+      <c r="C44" s="76" t="inlineStr">
+        <is>
+          <t>מוצאי שבת</t>
+        </is>
+      </c>
+      <c r="D44" s="68" t="inlineStr">
+        <is>
+          <t>טאטוא ושטיפת בית מיכאל</t>
+        </is>
+      </c>
+      <c r="E44" s="90" t="n"/>
+      <c r="F44" s="76" t="inlineStr">
+        <is>
+          <t>ניקיונות וארגון הקמפוס</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>בית מיכאל</t>
+        </is>
+      </c>
+      <c r="C45" s="76" t="inlineStr">
+        <is>
+          <t>מוצאי שבת</t>
+        </is>
+      </c>
+      <c r="D45" s="68" t="inlineStr">
+        <is>
+          <t>החזרת בית המדרש לסידור המקורי</t>
+        </is>
+      </c>
+      <c r="E45" s="90" t="n"/>
+      <c r="F45" s="76" t="inlineStr">
+        <is>
+          <t>ניקיונות וארגון הקמפוס</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>חדר אוכל</t>
+        </is>
+      </c>
+      <c r="C46" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D46" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור חדר אוכל</t>
+        </is>
+      </c>
+      <c r="E46" s="90" t="n"/>
+      <c r="F46" s="76" t="n"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>חדר אוכל</t>
+        </is>
+      </c>
+      <c r="C47" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D47" s="68" t="inlineStr">
+        <is>
+          <t>שטיפת רצפת חדר האוכל</t>
+        </is>
+      </c>
+      <c r="E47" s="90" t="n"/>
+      <c r="F47" s="76" t="n"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>שירותי חדר אוכל</t>
+        </is>
+      </c>
+      <c r="C48" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D48" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון שירותי חדר אוכל</t>
+        </is>
+      </c>
+      <c r="E48" s="90" t="n"/>
+      <c r="F48" s="76" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>שירותים כלליים</t>
+        </is>
+      </c>
+      <c r="C49" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D49" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון שירותים — אקונומיקה ונייר</t>
+        </is>
+      </c>
+      <c r="E49" s="90" t="n"/>
+      <c r="F49" s="76" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>מטבח</t>
+        </is>
+      </c>
+      <c r="C50" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D50" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון מטבח — כולל הכל</t>
+        </is>
+      </c>
+      <c r="E50" s="90" t="n"/>
+      <c r="F50" s="76" t="n"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>מטבח</t>
+        </is>
+      </c>
+      <c r="C51" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D51" s="68" t="inlineStr">
+        <is>
+          <t>כיריים וכיורים</t>
+        </is>
+      </c>
+      <c r="E51" s="90" t="n"/>
+      <c r="F51" s="76" t="n"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>מטבח</t>
+        </is>
+      </c>
+      <c r="C52" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D52" s="68" t="inlineStr">
+        <is>
+          <t>פינוי כלים מהייבוש וסידור מזווה</t>
+        </is>
+      </c>
+      <c r="E52" s="90" t="n"/>
+      <c r="F52" s="76" t="n"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>חדר מקררים</t>
+        </is>
+      </c>
+      <c r="C53" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D53" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור חדר מקררים</t>
+        </is>
+      </c>
+      <c r="E53" s="90" t="n"/>
+      <c r="F53" s="76" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>קוביה</t>
+        </is>
+      </c>
+      <c r="C54" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D54" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור הקוביה</t>
+        </is>
+      </c>
+      <c r="E54" s="90" t="n"/>
+      <c r="F54" s="76" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>מרחבי חבורות</t>
+        </is>
+      </c>
+      <c r="C55" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D55" s="68" t="inlineStr">
+        <is>
+          <t>סידור מרחבי החבורות — כיסאות לפי מספר החבורות</t>
+        </is>
+      </c>
+      <c r="E55" s="90" t="n"/>
+      <c r="F55" s="76" t="inlineStr">
+        <is>
+          <t>חבורות חניכים</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>מרפסת וחצר</t>
+        </is>
+      </c>
+      <c r="C56" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D56" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור המרפסת והחצר</t>
+        </is>
+      </c>
+      <c r="E56" s="90" t="n"/>
+      <c r="F56" s="76" t="n"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>כללי</t>
+        </is>
+      </c>
+      <c r="C57" s="76" t="inlineStr">
+        <is>
+          <t>מוצאי שבת</t>
+        </is>
+      </c>
+      <c r="D57" s="68" t="inlineStr">
+        <is>
+          <t>החזרת ספות ורהיטים למקומם</t>
+        </is>
+      </c>
+      <c r="E57" s="90" t="n"/>
+      <c r="F57" s="76" t="inlineStr">
+        <is>
+          <t>ניקיונות וארגון הקמפוס</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>חימום</t>
+        </is>
+      </c>
+      <c r="C58" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D58" s="68" t="inlineStr">
+        <is>
+          <t>הכנת פלטות חימום והדלקתן</t>
+        </is>
+      </c>
+      <c r="E58" s="90" t="n"/>
+      <c r="F58" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת בוקר שישי</t>
-        </is>
-      </c>
-      <c r="C21" s="76" t="inlineStr">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>חימום</t>
+        </is>
+      </c>
+      <c r="C59" s="76" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D21" s="68" t="inlineStr">
-        <is>
-          <t>הכנת ארוחת בוקר שישי וניקיון אחריה</t>
-        </is>
-      </c>
-      <c r="E21" s="76" t="inlineStr">
-        <is>
-          <t>שישי — ארוחת בוקר</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים שישי</t>
-        </is>
-      </c>
-      <c r="C22" s="76" t="inlineStr">
+      <c r="D59" s="68" t="inlineStr">
+        <is>
+          <t>הדלקת תנור החימום במטבח</t>
+        </is>
+      </c>
+      <c r="E59" s="90" t="n"/>
+      <c r="F59" s="76" t="inlineStr">
+        <is>
+          <t>שישי — הכנות ועבודה</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>חימום</t>
+        </is>
+      </c>
+      <c r="C60" s="76" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D22" s="68" t="inlineStr">
-        <is>
-          <t>הכנת ארוחת צהריים שישי וניקיון אחריה</t>
-        </is>
-      </c>
-      <c r="E22" s="76" t="inlineStr">
-        <is>
-          <t>שישי — ארוחת צהריים</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת ערב שבת</t>
-        </is>
-      </c>
-      <c r="C23" s="76" t="inlineStr">
+      <c r="D60" s="68" t="inlineStr">
+        <is>
+          <t>מילוי והדלקת מיחמים</t>
+        </is>
+      </c>
+      <c r="E60" s="90" t="n"/>
+      <c r="F60" s="76" t="inlineStr">
+        <is>
+          <t>שישי — הכנות ועבודה</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>חימום</t>
+        </is>
+      </c>
+      <c r="C61" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D61" s="68" t="inlineStr">
+        <is>
+          <t>לוודא שהאוכל על הפלטות בזמן</t>
+        </is>
+      </c>
+      <c r="E61" s="90" t="n"/>
+      <c r="F61" s="76" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>הבדלה</t>
+        </is>
+      </c>
+      <c r="C62" s="76" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D23" s="68" t="inlineStr">
-        <is>
-          <t>הכנסת אוכל מהקייטרינג לתנור חימום — כשעתיים לפני הקידוש</t>
-        </is>
-      </c>
-      <c r="E23" s="76" t="inlineStr">
-        <is>
-          <t>סעודת שבת</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת ערב שבת</t>
-        </is>
-      </c>
-      <c r="C24" s="76" t="inlineStr">
+      <c r="D62" s="68" t="inlineStr">
+        <is>
+          <t>הכנת ציוד הבדלה — נר, יין, בשמים</t>
+        </is>
+      </c>
+      <c r="E62" s="90" t="n"/>
+      <c r="F62" s="76" t="inlineStr">
+        <is>
+          <t>הבדלה</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>חשמל</t>
+        </is>
+      </c>
+      <c r="C63" s="76" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D24" s="68" t="inlineStr">
-        <is>
-          <t>הוצאת האוכל מהתנור אחרי הקידוש ולפני הסעודה</t>
-        </is>
-      </c>
-      <c r="E24" s="76" t="inlineStr">
-        <is>
-          <t>סעודת שבת</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת ערב שבת</t>
-        </is>
-      </c>
-      <c r="C25" s="76" t="inlineStr">
+      <c r="D63" s="68" t="inlineStr">
+        <is>
+          <t>הדלקת אורות ומזגנים לשבת וכיוון שעון שבת</t>
+        </is>
+      </c>
+      <c r="E63" s="90" t="n"/>
+      <c r="F63" s="76" t="inlineStr">
+        <is>
+          <t>שישי — הכנות ועבודה</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>עיתון</t>
+        </is>
+      </c>
+      <c r="C64" s="76" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D25" s="68" t="inlineStr">
-        <is>
-          <t>ארגון סלטים והכנת טחינה לשולחנות</t>
-        </is>
-      </c>
-      <c r="E25" s="76" t="inlineStr">
-        <is>
-          <t>סעודת שבת</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת ערב שבת</t>
-        </is>
-      </c>
-      <c r="C26" s="76" t="inlineStr">
+      <c r="D64" s="68" t="inlineStr">
+        <is>
+          <t>הכנת עיתון השבת והפצתו</t>
+        </is>
+      </c>
+      <c r="E64" s="90" t="n"/>
+      <c r="F64" s="76" t="inlineStr">
+        <is>
+          <t>שישי — הכנות ועבודה</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>מרחבים</t>
+        </is>
+      </c>
+      <c r="C65" s="76" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D26" s="68" t="inlineStr">
-        <is>
-          <t>עריכת שולחנות — כפות הגשה וחלוקת סלטים</t>
-        </is>
-      </c>
-      <c r="E26" s="76" t="inlineStr">
-        <is>
-          <t>סעודת שבת</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת ערב שבת</t>
-        </is>
-      </c>
-      <c r="C27" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D27" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון מרחב האוכל אחרי הסעודה</t>
-        </is>
-      </c>
-      <c r="E27" s="76" t="inlineStr">
-        <is>
-          <t>סעודת שבת</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C28" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D28" s="68" t="inlineStr">
-        <is>
-          <t>חימום האוכל הרלוונטי בלבד לקידוש על הפלטות</t>
-        </is>
-      </c>
-      <c r="E28" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C29" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D29" s="68" t="inlineStr">
-        <is>
-          <t>הכנסת מאפים לתנור חימום — ללא אלומיניום מעל העוגות</t>
-        </is>
-      </c>
-      <c r="E29" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C30" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D30" s="68" t="inlineStr">
-        <is>
-          <t>תיבול סלטים לקידוש</t>
-        </is>
-      </c>
-      <c r="E30" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C31" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D31" s="68" t="inlineStr">
-        <is>
-          <t>עריכת האוכל לקידוש</t>
-        </is>
-      </c>
-      <c r="E31" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C32" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D32" s="68" t="inlineStr">
-        <is>
-          <t>סידור פינת קפה — ניקוי, חלב, קפה וסוכר</t>
-        </is>
-      </c>
-      <c r="E32" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C33" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D33" s="68" t="inlineStr">
-        <is>
-          <t>הוצאת פירות חתוכים ועוגות</t>
-        </is>
-      </c>
-      <c r="E33" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C34" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D34" s="68" t="inlineStr">
-        <is>
-          <t>הוצאת כלים וסידור שולחנות במעגל</t>
-        </is>
-      </c>
-      <c r="E34" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C35" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D35" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון מרחב האוכל אחרי הקידוש</t>
-        </is>
-      </c>
-      <c r="E35" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C36" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D36" s="68" t="inlineStr">
-        <is>
-          <t>קיפול והכנסה למקרר בסיום — לא להשאיר אוכל פתוח</t>
-        </is>
-      </c>
-      <c r="E36" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים שבת</t>
-        </is>
-      </c>
-      <c r="C37" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D37" s="68" t="inlineStr">
-        <is>
-          <t>הכנסת אוכל מהקייטרינג לתנור חימום — כשעתיים לפני ארוחת הצהריים</t>
-        </is>
-      </c>
-      <c r="E37" s="76" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים שבת</t>
-        </is>
-      </c>
-      <c r="C38" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D38" s="68" t="inlineStr">
-        <is>
-          <t>עריכת שולחן לארוחת צהריים אחרי הקידוש</t>
-        </is>
-      </c>
-      <c r="E38" s="76" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים שבת</t>
-        </is>
-      </c>
-      <c r="C39" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D39" s="68" t="inlineStr">
-        <is>
-          <t>חלוקת סלטים לשולחנות</t>
-        </is>
-      </c>
-      <c r="E39" s="76" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים שבת</t>
-        </is>
-      </c>
-      <c r="C40" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D40" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון מרחב האוכל אחרי ארוחת הצהריים</t>
-        </is>
-      </c>
-      <c r="E40" s="76" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="inlineStr">
-        <is>
-          <t>סעודה שלישית</t>
-        </is>
-      </c>
-      <c r="C41" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D41" s="68" t="inlineStr">
-        <is>
-          <t>הכנסת מאפים לחימום והוצאת האוכל</t>
-        </is>
-      </c>
-      <c r="E41" s="76" t="inlineStr">
-        <is>
-          <t>סעודה שלישית</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="inlineStr">
-        <is>
-          <t>סעודה שלישית</t>
-        </is>
-      </c>
-      <c r="C42" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D42" s="68" t="inlineStr">
-        <is>
-          <t>עריכת המרחב וסידור בסיום</t>
-        </is>
-      </c>
-      <c r="E42" s="76" t="inlineStr">
-        <is>
-          <t>סעודה שלישית</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>טיש</t>
-        </is>
-      </c>
-      <c r="C43" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D43" s="68" t="inlineStr">
-        <is>
-          <t>סידור שולחנות וכיסאות לטיש</t>
-        </is>
-      </c>
-      <c r="E43" s="76" t="inlineStr">
-        <is>
-          <t>טיש עם איש צוות</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="inlineStr">
-        <is>
-          <t>טיש</t>
-        </is>
-      </c>
-      <c r="C44" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D44" s="68" t="inlineStr">
-        <is>
-          <t>הבאת שתייה וסידור כוסות</t>
-        </is>
-      </c>
-      <c r="E44" s="76" t="inlineStr">
-        <is>
-          <t>טיש עם איש צוות</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>טיש</t>
-        </is>
-      </c>
-      <c r="C45" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D45" s="68" t="inlineStr">
-        <is>
-          <t>חימום עוגות פרווה והוצאת כיבוד</t>
-        </is>
-      </c>
-      <c r="E45" s="76" t="inlineStr">
-        <is>
-          <t>טיש עם איש צוות</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="inlineStr">
-        <is>
-          <t>טיש</t>
-        </is>
-      </c>
-      <c r="C46" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D46" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון מלא בסיום הטיש</t>
-        </is>
-      </c>
-      <c r="E46" s="76" t="inlineStr">
-        <is>
-          <t>טיש עם איש צוות</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="inlineStr">
-        <is>
-          <t>בית מיכאל</t>
-        </is>
-      </c>
-      <c r="C47" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D47" s="68" t="inlineStr">
-        <is>
-          <t>הפיכת בית מיכאל לבית כנסת — מחיצה, שורות כיסאות משני הצדדים, סידורים על הכיסאות, הפעלת מזגן</t>
-        </is>
-      </c>
-      <c r="E47" s="76" t="inlineStr">
-        <is>
-          <t>קבלת שבת וערבית</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="inlineStr">
-        <is>
-          <t>בית מיכאל</t>
-        </is>
-      </c>
-      <c r="C48" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D48" s="68" t="inlineStr">
-        <is>
-          <t>הבאת ספות וסידור מרחב הטיש</t>
-        </is>
-      </c>
-      <c r="E48" s="76" t="inlineStr">
-        <is>
-          <t>טיש עם איש צוות</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t>בית מיכאל</t>
-        </is>
-      </c>
-      <c r="C49" s="76" t="inlineStr">
+      <c r="D65" s="68" t="inlineStr">
+        <is>
+          <t>פתיחת המרחבים והכנתם</t>
+        </is>
+      </c>
+      <c r="E65" s="90" t="n"/>
+      <c r="F65" s="76" t="inlineStr">
+        <is>
+          <t>שישי — הכנות ועבודה</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>חשמל</t>
+        </is>
+      </c>
+      <c r="C66" s="76" t="inlineStr">
         <is>
           <t>מוצאי שבת</t>
         </is>
       </c>
-      <c r="D49" s="68" t="inlineStr">
-        <is>
-          <t>טאטוא ושטיפת בית מיכאל</t>
-        </is>
-      </c>
-      <c r="E49" s="76" t="inlineStr">
+      <c r="D66" s="68" t="inlineStr">
+        <is>
+          <t>כיבוי פלטות, מיחמים ותנור חימום</t>
+        </is>
+      </c>
+      <c r="E66" s="90" t="n"/>
+      <c r="F66" s="76" t="inlineStr">
         <is>
           <t>ניקיונות וארגון הקמפוס</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B50" s="20" t="inlineStr">
-        <is>
-          <t>בית מיכאל</t>
-        </is>
-      </c>
-      <c r="C50" s="76" t="inlineStr">
-        <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
-      <c r="D50" s="68" t="inlineStr">
-        <is>
-          <t>החזרת בית המדרש לסידור המקורי</t>
-        </is>
-      </c>
-      <c r="E50" s="76" t="inlineStr">
-        <is>
-          <t>ניקיונות וארגון הקמפוס</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>חדר אוכל</t>
-        </is>
-      </c>
-      <c r="C51" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D51" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור חדר אוכל</t>
-        </is>
-      </c>
-      <c r="E51" s="76" t="n"/>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B52" s="20" t="inlineStr">
-        <is>
-          <t>חדר אוכל</t>
-        </is>
-      </c>
-      <c r="C52" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D52" s="68" t="inlineStr">
-        <is>
-          <t>שטיפת רצפת חדר האוכל</t>
-        </is>
-      </c>
-      <c r="E52" s="76" t="n"/>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B53" s="20" t="inlineStr">
-        <is>
-          <t>שירותי חדר אוכל</t>
-        </is>
-      </c>
-      <c r="C53" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D53" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון שירותי חדר אוכל</t>
-        </is>
-      </c>
-      <c r="E53" s="76" t="n"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B54" s="20" t="inlineStr">
-        <is>
-          <t>שירותים כלליים</t>
-        </is>
-      </c>
-      <c r="C54" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D54" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון שירותים — אקונומיקה ונייר</t>
-        </is>
-      </c>
-      <c r="E54" s="76" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="inlineStr">
-        <is>
-          <t>מטבח</t>
-        </is>
-      </c>
-      <c r="C55" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D55" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון מטבח — כולל הכל</t>
-        </is>
-      </c>
-      <c r="E55" s="76" t="n"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B56" s="20" t="inlineStr">
-        <is>
-          <t>מטבח</t>
-        </is>
-      </c>
-      <c r="C56" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D56" s="68" t="inlineStr">
-        <is>
-          <t>כיריים וכיורים</t>
-        </is>
-      </c>
-      <c r="E56" s="76" t="n"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B57" s="20" t="inlineStr">
-        <is>
-          <t>מטבח</t>
-        </is>
-      </c>
-      <c r="C57" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D57" s="68" t="inlineStr">
-        <is>
-          <t>פינוי כלים מהייבוש וסידור מזווה</t>
-        </is>
-      </c>
-      <c r="E57" s="76" t="n"/>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B58" s="20" t="inlineStr">
-        <is>
-          <t>חדר מקררים</t>
-        </is>
-      </c>
-      <c r="C58" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D58" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור חדר מקררים</t>
-        </is>
-      </c>
-      <c r="E58" s="76" t="n"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B59" s="20" t="inlineStr">
-        <is>
-          <t>קוביה</t>
-        </is>
-      </c>
-      <c r="C59" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D59" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור הקוביה</t>
-        </is>
-      </c>
-      <c r="E59" s="76" t="n"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B60" s="20" t="inlineStr">
-        <is>
-          <t>מרחבי חבורות</t>
-        </is>
-      </c>
-      <c r="C60" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D60" s="68" t="inlineStr">
-        <is>
-          <t>סידור מרחבי החבורות — כיסאות לפי מספר החבורות</t>
-        </is>
-      </c>
-      <c r="E60" s="76" t="inlineStr">
-        <is>
-          <t>חבורות חניכים</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B61" s="20" t="inlineStr">
-        <is>
-          <t>מרפסת וחצר</t>
-        </is>
-      </c>
-      <c r="C61" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D61" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור המרפסת והחצר</t>
-        </is>
-      </c>
-      <c r="E61" s="76" t="n"/>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B62" s="20" t="inlineStr">
-        <is>
-          <t>כללי</t>
-        </is>
-      </c>
-      <c r="C62" s="76" t="inlineStr">
-        <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
-      <c r="D62" s="68" t="inlineStr">
-        <is>
-          <t>החזרת ספות ורהיטים למקומם</t>
-        </is>
-      </c>
-      <c r="E62" s="76" t="inlineStr">
-        <is>
-          <t>ניקיונות וארגון הקמפוס</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B63" s="20" t="inlineStr">
-        <is>
-          <t>חימום</t>
-        </is>
-      </c>
-      <c r="C63" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D63" s="68" t="inlineStr">
-        <is>
-          <t>הכנת פלטות חימום והדלקתן</t>
-        </is>
-      </c>
-      <c r="E63" s="76" t="inlineStr">
-        <is>
-          <t>שישי — הכנות ועבודה</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B64" s="20" t="inlineStr">
-        <is>
-          <t>חימום</t>
-        </is>
-      </c>
-      <c r="C64" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D64" s="68" t="inlineStr">
-        <is>
-          <t>הדלקת תנור החימום במטבח</t>
-        </is>
-      </c>
-      <c r="E64" s="76" t="inlineStr">
-        <is>
-          <t>שישי — הכנות ועבודה</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B65" s="20" t="inlineStr">
-        <is>
-          <t>חימום</t>
-        </is>
-      </c>
-      <c r="C65" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D65" s="68" t="inlineStr">
-        <is>
-          <t>מילוי והדלקת מיחמים</t>
-        </is>
-      </c>
-      <c r="E65" s="76" t="inlineStr">
-        <is>
-          <t>שישי — הכנות ועבודה</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B66" s="20" t="inlineStr">
-        <is>
-          <t>חימום</t>
-        </is>
-      </c>
-      <c r="C66" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D66" s="68" t="inlineStr">
-        <is>
-          <t>לוודא שהאוכל על הפלטות בזמן</t>
-        </is>
-      </c>
-      <c r="E66" s="76" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
-    </row>
     <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B67" s="20" t="inlineStr">
-        <is>
-          <t>הבדלה</t>
-        </is>
-      </c>
-      <c r="C67" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D67" s="68" t="inlineStr">
-        <is>
-          <t>הכנת ציוד הבדלה — נר, יין, בשמים</t>
-        </is>
-      </c>
-      <c r="E67" s="76" t="inlineStr">
-        <is>
-          <t>הבדלה</t>
-        </is>
-      </c>
+      <c r="A67" s="19" t="n"/>
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="76" t="n"/>
+      <c r="D67" s="68" t="n"/>
+      <c r="E67" s="90" t="n"/>
+      <c r="F67" s="76" t="n"/>
     </row>
     <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B68" s="20" t="inlineStr">
-        <is>
-          <t>חשמל</t>
-        </is>
-      </c>
-      <c r="C68" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D68" s="68" t="inlineStr">
-        <is>
-          <t>הדלקת אורות ומזגנים לשבת וכיוון שעון שבת</t>
-        </is>
-      </c>
-      <c r="E68" s="76" t="inlineStr">
-        <is>
-          <t>שישי — הכנות ועבודה</t>
-        </is>
-      </c>
+      <c r="A68" s="19" t="n"/>
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="76" t="n"/>
+      <c r="D68" s="68" t="n"/>
+      <c r="E68" s="90" t="n"/>
+      <c r="F68" s="76" t="n"/>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B69" s="20" t="inlineStr">
-        <is>
-          <t>עיתון</t>
-        </is>
-      </c>
-      <c r="C69" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D69" s="68" t="inlineStr">
-        <is>
-          <t>הכנת עיתון השבת והפצתו</t>
-        </is>
-      </c>
-      <c r="E69" s="76" t="inlineStr">
-        <is>
-          <t>שישי — הכנות ועבודה</t>
-        </is>
-      </c>
+      <c r="A69" s="19" t="n"/>
+      <c r="B69" s="20" t="n"/>
+      <c r="C69" s="76" t="n"/>
+      <c r="D69" s="68" t="n"/>
+      <c r="E69" s="90" t="n"/>
+      <c r="F69" s="76" t="n"/>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B70" s="20" t="inlineStr">
-        <is>
-          <t>מרחבים</t>
-        </is>
-      </c>
-      <c r="C70" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D70" s="68" t="inlineStr">
-        <is>
-          <t>פתיחת המרחבים והכנתם</t>
-        </is>
-      </c>
-      <c r="E70" s="76" t="inlineStr">
-        <is>
-          <t>שישי — הכנות ועבודה</t>
-        </is>
-      </c>
+      <c r="A70" s="19" t="n"/>
+      <c r="B70" s="20" t="n"/>
+      <c r="C70" s="76" t="n"/>
+      <c r="D70" s="68" t="n"/>
+      <c r="E70" s="90" t="n"/>
+      <c r="F70" s="76" t="n"/>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="inlineStr">
-        <is>
-          <t>חשמל</t>
-        </is>
-      </c>
-      <c r="C71" s="76" t="inlineStr">
-        <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
-      <c r="D71" s="68" t="inlineStr">
-        <is>
-          <t>כיבוי פלטות, מיחמים ותנור חימום</t>
-        </is>
-      </c>
-      <c r="E71" s="76" t="inlineStr">
-        <is>
-          <t>ניקיונות וארגון הקמפוס</t>
-        </is>
-      </c>
+      <c r="A71" s="19" t="n"/>
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="76" t="n"/>
+      <c r="D71" s="68" t="n"/>
+      <c r="E71" s="90" t="n"/>
+      <c r="F71" s="76" t="n"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="19" t="n"/>
       <c r="B72" s="20" t="n"/>
       <c r="C72" s="76" t="n"/>
       <c r="D72" s="68" t="n"/>
-      <c r="E72" s="76" t="n"/>
+      <c r="E72" s="90" t="n"/>
+      <c r="F72" s="76" t="n"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="19" t="n"/>
       <c r="B73" s="20" t="n"/>
       <c r="C73" s="76" t="n"/>
       <c r="D73" s="68" t="n"/>
-      <c r="E73" s="76" t="n"/>
+      <c r="E73" s="90" t="n"/>
+      <c r="F73" s="76" t="n"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="19" t="n"/>
       <c r="B74" s="20" t="n"/>
       <c r="C74" s="76" t="n"/>
       <c r="D74" s="68" t="n"/>
-      <c r="E74" s="76" t="n"/>
+      <c r="E74" s="90" t="n"/>
+      <c r="F74" s="76" t="n"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="19" t="n"/>
       <c r="B75" s="20" t="n"/>
       <c r="C75" s="76" t="n"/>
       <c r="D75" s="68" t="n"/>
-      <c r="E75" s="76" t="n"/>
+      <c r="E75" s="90" t="n"/>
+      <c r="F75" s="76" t="n"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="19" t="n"/>
       <c r="B76" s="20" t="n"/>
       <c r="C76" s="76" t="n"/>
       <c r="D76" s="68" t="n"/>
-      <c r="E76" s="76" t="n"/>
+      <c r="E76" s="90" t="n"/>
+      <c r="F76" s="76" t="n"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="19" t="n"/>
       <c r="B77" s="20" t="n"/>
       <c r="C77" s="76" t="n"/>
       <c r="D77" s="68" t="n"/>
-      <c r="E77" s="76" t="n"/>
+      <c r="E77" s="90" t="n"/>
+      <c r="F77" s="76" t="n"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="19" t="n"/>
       <c r="B78" s="20" t="n"/>
       <c r="C78" s="76" t="n"/>
       <c r="D78" s="68" t="n"/>
-      <c r="E78" s="76" t="n"/>
+      <c r="E78" s="90" t="n"/>
+      <c r="F78" s="76" t="n"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="19" t="n"/>
       <c r="B79" s="20" t="n"/>
       <c r="C79" s="76" t="n"/>
       <c r="D79" s="68" t="n"/>
-      <c r="E79" s="76" t="n"/>
+      <c r="E79" s="90" t="n"/>
+      <c r="F79" s="76" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="19" t="n"/>
       <c r="B80" s="20" t="n"/>
       <c r="C80" s="76" t="n"/>
       <c r="D80" s="68" t="n"/>
-      <c r="E80" s="76" t="n"/>
+      <c r="E80" s="90" t="n"/>
+      <c r="F80" s="76" t="n"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="19" t="n"/>
       <c r="B81" s="20" t="n"/>
       <c r="C81" s="76" t="n"/>
       <c r="D81" s="68" t="n"/>
-      <c r="E81" s="76" t="n"/>
+      <c r="E81" s="90" t="n"/>
+      <c r="F81" s="76" t="n"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="19" t="n"/>
       <c r="B82" s="20" t="n"/>
       <c r="C82" s="76" t="n"/>
       <c r="D82" s="68" t="n"/>
-      <c r="E82" s="76" t="n"/>
+      <c r="E82" s="90" t="n"/>
+      <c r="F82" s="76" t="n"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="19" t="n"/>
       <c r="B83" s="20" t="n"/>
       <c r="C83" s="76" t="n"/>
       <c r="D83" s="68" t="n"/>
-      <c r="E83" s="76" t="n"/>
+      <c r="E83" s="90" t="n"/>
+      <c r="F83" s="76" t="n"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="19" t="n"/>
       <c r="B84" s="20" t="n"/>
       <c r="C84" s="76" t="n"/>
       <c r="D84" s="68" t="n"/>
-      <c r="E84" s="76" t="n"/>
+      <c r="E84" s="90" t="n"/>
+      <c r="F84" s="76" t="n"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="19" t="n"/>
       <c r="B85" s="20" t="n"/>
       <c r="C85" s="76" t="n"/>
       <c r="D85" s="68" t="n"/>
-      <c r="E85" s="76" t="n"/>
+      <c r="E85" s="90" t="n"/>
+      <c r="F85" s="76" t="n"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="19" t="n"/>
       <c r="B86" s="20" t="n"/>
       <c r="C86" s="76" t="n"/>
       <c r="D86" s="68" t="n"/>
-      <c r="E86" s="76" t="n"/>
+      <c r="E86" s="90" t="n"/>
+      <c r="F86" s="76" t="n"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="19" t="n"/>
       <c r="B87" s="20" t="n"/>
       <c r="C87" s="76" t="n"/>
       <c r="D87" s="68" t="n"/>
-      <c r="E87" s="76" t="n"/>
+      <c r="E87" s="90" t="n"/>
+      <c r="F87" s="76" t="n"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="19" t="n"/>
       <c r="B88" s="20" t="n"/>
       <c r="C88" s="76" t="n"/>
       <c r="D88" s="68" t="n"/>
-      <c r="E88" s="76" t="n"/>
+      <c r="E88" s="90" t="n"/>
+      <c r="F88" s="76" t="n"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="19" t="n"/>
       <c r="B89" s="20" t="n"/>
       <c r="C89" s="76" t="n"/>
       <c r="D89" s="68" t="n"/>
-      <c r="E89" s="76" t="n"/>
+      <c r="E89" s="90" t="n"/>
+      <c r="F89" s="76" t="n"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="19" t="n"/>
       <c r="B90" s="20" t="n"/>
       <c r="C90" s="76" t="n"/>
       <c r="D90" s="68" t="n"/>
-      <c r="E90" s="76" t="n"/>
+      <c r="E90" s="90" t="n"/>
+      <c r="F90" s="76" t="n"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="19" t="n"/>
       <c r="B91" s="20" t="n"/>
       <c r="C91" s="76" t="n"/>
       <c r="D91" s="68" t="n"/>
-      <c r="E91" s="76" t="n"/>
+      <c r="E91" s="90" t="n"/>
+      <c r="F91" s="76" t="n"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="19" t="n"/>
       <c r="B92" s="20" t="n"/>
       <c r="C92" s="76" t="n"/>
       <c r="D92" s="68" t="n"/>
-      <c r="E92" s="76" t="n"/>
+      <c r="E92" s="90" t="n"/>
+      <c r="F92" s="76" t="n"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="19" t="n"/>
       <c r="B93" s="20" t="n"/>
       <c r="C93" s="76" t="n"/>
       <c r="D93" s="68" t="n"/>
-      <c r="E93" s="76" t="n"/>
+      <c r="E93" s="90" t="n"/>
+      <c r="F93" s="76" t="n"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="19" t="n"/>
       <c r="B94" s="20" t="n"/>
       <c r="C94" s="76" t="n"/>
       <c r="D94" s="68" t="n"/>
-      <c r="E94" s="76" t="n"/>
+      <c r="E94" s="90" t="n"/>
+      <c r="F94" s="76" t="n"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="19" t="n"/>
       <c r="B95" s="20" t="n"/>
       <c r="C95" s="76" t="n"/>
       <c r="D95" s="68" t="n"/>
-      <c r="E95" s="76" t="n"/>
+      <c r="E95" s="90" t="n"/>
+      <c r="F95" s="76" t="n"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="19" t="n"/>
       <c r="B96" s="20" t="n"/>
       <c r="C96" s="76" t="n"/>
       <c r="D96" s="68" t="n"/>
-      <c r="E96" s="76" t="n"/>
+      <c r="E96" s="90" t="n"/>
+      <c r="F96" s="76" t="n"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="19" t="n"/>
       <c r="B97" s="20" t="n"/>
       <c r="C97" s="76" t="n"/>
       <c r="D97" s="68" t="n"/>
-      <c r="E97" s="76" t="n"/>
+      <c r="E97" s="90" t="n"/>
+      <c r="F97" s="76" t="n"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="19" t="n"/>
       <c r="B98" s="20" t="n"/>
       <c r="C98" s="76" t="n"/>
       <c r="D98" s="68" t="n"/>
-      <c r="E98" s="76" t="n"/>
+      <c r="E98" s="90" t="n"/>
+      <c r="F98" s="76" t="n"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="19" t="n"/>
       <c r="B99" s="20" t="n"/>
       <c r="C99" s="76" t="n"/>
       <c r="D99" s="68" t="n"/>
-      <c r="E99" s="76" t="n"/>
+      <c r="E99" s="90" t="n"/>
+      <c r="F99" s="76" t="n"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="19" t="n"/>
       <c r="B100" s="20" t="n"/>
       <c r="C100" s="76" t="n"/>
       <c r="D100" s="68" t="n"/>
-      <c r="E100" s="76" t="n"/>
+      <c r="E100" s="90" t="n"/>
+      <c r="F100" s="76" t="n"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="19" t="n"/>
       <c r="B101" s="20" t="n"/>
       <c r="C101" s="76" t="n"/>
       <c r="D101" s="68" t="n"/>
-      <c r="E101" s="76" t="n"/>
+      <c r="E101" s="90" t="n"/>
+      <c r="F101" s="76" t="n"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="19" t="n"/>
       <c r="B102" s="20" t="n"/>
       <c r="C102" s="76" t="n"/>
       <c r="D102" s="68" t="n"/>
-      <c r="E102" s="76" t="n"/>
+      <c r="E102" s="90" t="n"/>
+      <c r="F102" s="76" t="n"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="19" t="n"/>
       <c r="B103" s="20" t="n"/>
       <c r="C103" s="76" t="n"/>
       <c r="D103" s="68" t="n"/>
-      <c r="E103" s="76" t="n"/>
+      <c r="E103" s="90" t="n"/>
+      <c r="F103" s="76" t="n"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="19" t="n"/>
       <c r="B104" s="20" t="n"/>
       <c r="C104" s="76" t="n"/>
       <c r="D104" s="68" t="n"/>
-      <c r="E104" s="76" t="n"/>
+      <c r="E104" s="90" t="n"/>
+      <c r="F104" s="76" t="n"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="19" t="n"/>
       <c r="B105" s="20" t="n"/>
       <c r="C105" s="76" t="n"/>
       <c r="D105" s="68" t="n"/>
-      <c r="E105" s="76" t="n"/>
+      <c r="E105" s="90" t="n"/>
+      <c r="F105" s="76" t="n"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="19" t="n"/>
       <c r="B106" s="20" t="n"/>
       <c r="C106" s="76" t="n"/>
       <c r="D106" s="68" t="n"/>
-      <c r="E106" s="76" t="n"/>
+      <c r="E106" s="90" t="n"/>
+      <c r="F106" s="76" t="n"/>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="19" t="n"/>
       <c r="B107" s="20" t="n"/>
       <c r="C107" s="76" t="n"/>
       <c r="D107" s="68" t="n"/>
-      <c r="E107" s="76" t="n"/>
+      <c r="E107" s="90" t="n"/>
+      <c r="F107" s="76" t="n"/>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="19" t="n"/>
       <c r="B108" s="20" t="n"/>
       <c r="C108" s="76" t="n"/>
       <c r="D108" s="68" t="n"/>
-      <c r="E108" s="76" t="n"/>
+      <c r="E108" s="90" t="n"/>
+      <c r="F108" s="76" t="n"/>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="19" t="n"/>
       <c r="B109" s="20" t="n"/>
       <c r="C109" s="76" t="n"/>
       <c r="D109" s="68" t="n"/>
-      <c r="E109" s="76" t="n"/>
+      <c r="E109" s="90" t="n"/>
+      <c r="F109" s="76" t="n"/>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="19" t="n"/>
       <c r="B110" s="20" t="n"/>
       <c r="C110" s="76" t="n"/>
       <c r="D110" s="68" t="n"/>
-      <c r="E110" s="76" t="n"/>
+      <c r="E110" s="90" t="n"/>
+      <c r="F110" s="76" t="n"/>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="19" t="n"/>
       <c r="B111" s="20" t="n"/>
       <c r="C111" s="76" t="n"/>
       <c r="D111" s="68" t="n"/>
-      <c r="E111" s="76" t="n"/>
+      <c r="E111" s="90" t="n"/>
+      <c r="F111" s="76" t="n"/>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="19" t="n"/>
       <c r="B112" s="20" t="n"/>
       <c r="C112" s="76" t="n"/>
       <c r="D112" s="68" t="n"/>
-      <c r="E112" s="76" t="n"/>
+      <c r="E112" s="90" t="n"/>
+      <c r="F112" s="76" t="n"/>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="19" t="n"/>
       <c r="B113" s="20" t="n"/>
       <c r="C113" s="76" t="n"/>
       <c r="D113" s="68" t="n"/>
-      <c r="E113" s="76" t="n"/>
+      <c r="E113" s="90" t="n"/>
+      <c r="F113" s="76" t="n"/>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="19" t="n"/>
       <c r="B114" s="20" t="n"/>
       <c r="C114" s="76" t="n"/>
       <c r="D114" s="68" t="n"/>
-      <c r="E114" s="76" t="n"/>
+      <c r="E114" s="90" t="n"/>
+      <c r="F114" s="76" t="n"/>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="19" t="n"/>
       <c r="B115" s="20" t="n"/>
       <c r="C115" s="76" t="n"/>
       <c r="D115" s="68" t="n"/>
-      <c r="E115" s="76" t="n"/>
+      <c r="E115" s="90" t="n"/>
+      <c r="F115" s="76" t="n"/>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="19" t="n"/>
       <c r="B116" s="20" t="n"/>
       <c r="C116" s="76" t="n"/>
       <c r="D116" s="68" t="n"/>
-      <c r="E116" s="76" t="n"/>
+      <c r="E116" s="90" t="n"/>
+      <c r="F116" s="76" t="n"/>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="19" t="n"/>
       <c r="B117" s="20" t="n"/>
       <c r="C117" s="76" t="n"/>
       <c r="D117" s="68" t="n"/>
-      <c r="E117" s="76" t="n"/>
+      <c r="E117" s="90" t="n"/>
+      <c r="F117" s="76" t="n"/>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="19" t="n"/>
       <c r="B118" s="20" t="n"/>
       <c r="C118" s="76" t="n"/>
       <c r="D118" s="68" t="n"/>
-      <c r="E118" s="76" t="n"/>
+      <c r="E118" s="90" t="n"/>
+      <c r="F118" s="76" t="n"/>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="19" t="n"/>
       <c r="B119" s="20" t="n"/>
       <c r="C119" s="76" t="n"/>
       <c r="D119" s="68" t="n"/>
-      <c r="E119" s="76" t="n"/>
+      <c r="E119" s="90" t="n"/>
+      <c r="F119" s="76" t="n"/>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="19" t="n"/>
       <c r="B120" s="20" t="n"/>
       <c r="C120" s="76" t="n"/>
       <c r="D120" s="68" t="n"/>
-      <c r="E120" s="76" t="n"/>
+      <c r="E120" s="90" t="n"/>
+      <c r="F120" s="76" t="n"/>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="19" t="n"/>
       <c r="B121" s="20" t="n"/>
       <c r="C121" s="76" t="n"/>
       <c r="D121" s="68" t="n"/>
-      <c r="E121" s="76" t="n"/>
+      <c r="E121" s="90" t="n"/>
+      <c r="F121" s="76" t="n"/>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="19" t="n"/>
       <c r="B122" s="20" t="n"/>
       <c r="C122" s="76" t="n"/>
       <c r="D122" s="68" t="n"/>
-      <c r="E122" s="76" t="n"/>
+      <c r="E122" s="90" t="n"/>
+      <c r="F122" s="76" t="n"/>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="19" t="n"/>
       <c r="B123" s="20" t="n"/>
       <c r="C123" s="76" t="n"/>
       <c r="D123" s="68" t="n"/>
-      <c r="E123" s="76" t="n"/>
+      <c r="E123" s="90" t="n"/>
+      <c r="F123" s="76" t="n"/>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="19" t="n"/>
       <c r="B124" s="20" t="n"/>
       <c r="C124" s="76" t="n"/>
       <c r="D124" s="68" t="n"/>
-      <c r="E124" s="76" t="n"/>
+      <c r="E124" s="90" t="n"/>
+      <c r="F124" s="76" t="n"/>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="19" t="n"/>
       <c r="B125" s="20" t="n"/>
       <c r="C125" s="76" t="n"/>
       <c r="D125" s="68" t="n"/>
-      <c r="E125" s="76" t="n"/>
+      <c r="E125" s="90" t="n"/>
+      <c r="F125" s="76" t="n"/>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="19" t="n"/>
       <c r="B126" s="20" t="n"/>
       <c r="C126" s="76" t="n"/>
       <c r="D126" s="68" t="n"/>
-      <c r="E126" s="76" t="n"/>
+      <c r="E126" s="90" t="n"/>
+      <c r="F126" s="76" t="n"/>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="19" t="n"/>
       <c r="B127" s="20" t="n"/>
       <c r="C127" s="76" t="n"/>
       <c r="D127" s="68" t="n"/>
-      <c r="E127" s="76" t="n"/>
+      <c r="E127" s="90" t="n"/>
+      <c r="F127" s="76" t="n"/>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="19" t="n"/>
       <c r="B128" s="20" t="n"/>
       <c r="C128" s="76" t="n"/>
       <c r="D128" s="68" t="n"/>
-      <c r="E128" s="76" t="n"/>
+      <c r="E128" s="90" t="n"/>
+      <c r="F128" s="76" t="n"/>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="19" t="n"/>
       <c r="B129" s="20" t="n"/>
       <c r="C129" s="76" t="n"/>
       <c r="D129" s="68" t="n"/>
-      <c r="E129" s="76" t="n"/>
+      <c r="E129" s="90" t="n"/>
+      <c r="F129" s="76" t="n"/>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="19" t="n"/>
       <c r="B130" s="20" t="n"/>
       <c r="C130" s="76" t="n"/>
       <c r="D130" s="68" t="n"/>
-      <c r="E130" s="76" t="n"/>
+      <c r="E130" s="90" t="n"/>
+      <c r="F130" s="76" t="n"/>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="19" t="n"/>
       <c r="B131" s="20" t="n"/>
       <c r="C131" s="76" t="n"/>
       <c r="D131" s="68" t="n"/>
-      <c r="E131" s="76" t="n"/>
+      <c r="E131" s="90" t="n"/>
+      <c r="F131" s="76" t="n"/>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="19" t="n"/>
       <c r="B132" s="20" t="n"/>
       <c r="C132" s="76" t="n"/>
       <c r="D132" s="68" t="n"/>
-      <c r="E132" s="76" t="n"/>
+      <c r="E132" s="90" t="n"/>
+      <c r="F132" s="76" t="n"/>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="19" t="n"/>
       <c r="B133" s="20" t="n"/>
       <c r="C133" s="76" t="n"/>
       <c r="D133" s="68" t="n"/>
-      <c r="E133" s="76" t="n"/>
+      <c r="E133" s="90" t="n"/>
+      <c r="F133" s="76" t="n"/>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="19" t="n"/>
       <c r="B134" s="20" t="n"/>
       <c r="C134" s="76" t="n"/>
       <c r="D134" s="68" t="n"/>
-      <c r="E134" s="76" t="n"/>
+      <c r="E134" s="90" t="n"/>
+      <c r="F134" s="76" t="n"/>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="19" t="n"/>
       <c r="B135" s="20" t="n"/>
       <c r="C135" s="76" t="n"/>
       <c r="D135" s="68" t="n"/>
-      <c r="E135" s="76" t="n"/>
+      <c r="E135" s="90" t="n"/>
+      <c r="F135" s="76" t="n"/>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="19" t="n"/>
       <c r="B136" s="20" t="n"/>
       <c r="C136" s="76" t="n"/>
       <c r="D136" s="68" t="n"/>
-      <c r="E136" s="76" t="n"/>
+      <c r="E136" s="90" t="n"/>
+      <c r="F136" s="76" t="n"/>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="19" t="n"/>
       <c r="B137" s="20" t="n"/>
       <c r="C137" s="76" t="n"/>
       <c r="D137" s="68" t="n"/>
-      <c r="E137" s="76" t="n"/>
+      <c r="E137" s="90" t="n"/>
+      <c r="F137" s="76" t="n"/>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="19" t="n"/>
       <c r="B138" s="20" t="n"/>
       <c r="C138" s="76" t="n"/>
       <c r="D138" s="68" t="n"/>
-      <c r="E138" s="76" t="n"/>
+      <c r="E138" s="90" t="n"/>
+      <c r="F138" s="76" t="n"/>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="19" t="n"/>
       <c r="B139" s="20" t="n"/>
       <c r="C139" s="76" t="n"/>
       <c r="D139" s="68" t="n"/>
-      <c r="E139" s="76" t="n"/>
+      <c r="E139" s="90" t="n"/>
+      <c r="F139" s="76" t="n"/>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="19" t="n"/>
       <c r="B140" s="20" t="n"/>
       <c r="C140" s="76" t="n"/>
       <c r="D140" s="68" t="n"/>
-      <c r="E140" s="76" t="n"/>
+      <c r="E140" s="90" t="n"/>
+      <c r="F140" s="76" t="n"/>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="19" t="n"/>
       <c r="B141" s="20" t="n"/>
       <c r="C141" s="76" t="n"/>
       <c r="D141" s="68" t="n"/>
-      <c r="E141" s="76" t="n"/>
+      <c r="E141" s="90" t="n"/>
+      <c r="F141" s="76" t="n"/>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="19" t="n"/>
       <c r="B142" s="20" t="n"/>
       <c r="C142" s="76" t="n"/>
       <c r="D142" s="68" t="n"/>
-      <c r="E142" s="76" t="n"/>
+      <c r="E142" s="90" t="n"/>
+      <c r="F142" s="76" t="n"/>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="19" t="n"/>
       <c r="B143" s="20" t="n"/>
       <c r="C143" s="76" t="n"/>
       <c r="D143" s="68" t="n"/>
-      <c r="E143" s="76" t="n"/>
+      <c r="E143" s="90" t="n"/>
+      <c r="F143" s="76" t="n"/>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="19" t="n"/>
       <c r="B144" s="20" t="n"/>
       <c r="C144" s="76" t="n"/>
       <c r="D144" s="68" t="n"/>
-      <c r="E144" s="76" t="n"/>
+      <c r="E144" s="90" t="n"/>
+      <c r="F144" s="76" t="n"/>
     </row>
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="19" t="n"/>
       <c r="B145" s="20" t="n"/>
       <c r="C145" s="76" t="n"/>
       <c r="D145" s="68" t="n"/>
-      <c r="E145" s="76" t="n"/>
+      <c r="E145" s="90" t="n"/>
+      <c r="F145" s="76" t="n"/>
     </row>
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="19" t="n"/>
       <c r="B146" s="20" t="n"/>
       <c r="C146" s="76" t="n"/>
       <c r="D146" s="68" t="n"/>
-      <c r="E146" s="76" t="n"/>
+      <c r="E146" s="90" t="n"/>
+      <c r="F146" s="76" t="n"/>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="19" t="n"/>
       <c r="B147" s="20" t="n"/>
       <c r="C147" s="76" t="n"/>
       <c r="D147" s="68" t="n"/>
-      <c r="E147" s="76" t="n"/>
+      <c r="E147" s="90" t="n"/>
+      <c r="F147" s="76" t="n"/>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="19" t="n"/>
       <c r="B148" s="20" t="n"/>
       <c r="C148" s="76" t="n"/>
       <c r="D148" s="68" t="n"/>
-      <c r="E148" s="76" t="n"/>
+      <c r="E148" s="90" t="n"/>
+      <c r="F148" s="76" t="n"/>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="19" t="n"/>
       <c r="B149" s="20" t="n"/>
       <c r="C149" s="76" t="n"/>
       <c r="D149" s="68" t="n"/>
-      <c r="E149" s="76" t="n"/>
+      <c r="E149" s="90" t="n"/>
+      <c r="F149" s="76" t="n"/>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="19" t="n"/>
       <c r="B150" s="20" t="n"/>
       <c r="C150" s="76" t="n"/>
       <c r="D150" s="68" t="n"/>
-      <c r="E150" s="76" t="n"/>
+      <c r="E150" s="90" t="n"/>
+      <c r="F150" s="76" t="n"/>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="19" t="n"/>
       <c r="B151" s="20" t="n"/>
       <c r="C151" s="76" t="n"/>
       <c r="D151" s="68" t="n"/>
-      <c r="E151" s="76" t="n"/>
+      <c r="E151" s="90" t="n"/>
+      <c r="F151" s="76" t="n"/>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="19" t="n"/>
       <c r="B152" s="20" t="n"/>
       <c r="C152" s="76" t="n"/>
       <c r="D152" s="68" t="n"/>
-      <c r="E152" s="76" t="n"/>
+      <c r="E152" s="90" t="n"/>
+      <c r="F152" s="76" t="n"/>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="19" t="n"/>
       <c r="B153" s="20" t="n"/>
       <c r="C153" s="76" t="n"/>
       <c r="D153" s="68" t="n"/>
-      <c r="E153" s="76" t="n"/>
+      <c r="E153" s="90" t="n"/>
+      <c r="F153" s="76" t="n"/>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="19" t="n"/>
       <c r="B154" s="20" t="n"/>
       <c r="C154" s="76" t="n"/>
       <c r="D154" s="68" t="n"/>
-      <c r="E154" s="76" t="n"/>
+      <c r="E154" s="90" t="n"/>
+      <c r="F154" s="76" t="n"/>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="19" t="n"/>
       <c r="B155" s="20" t="n"/>
       <c r="C155" s="76" t="n"/>
       <c r="D155" s="68" t="n"/>
-      <c r="E155" s="76" t="n"/>
+      <c r="E155" s="90" t="n"/>
+      <c r="F155" s="76" t="n"/>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="19" t="n"/>
       <c r="B156" s="20" t="n"/>
       <c r="C156" s="76" t="n"/>
       <c r="D156" s="68" t="n"/>
-      <c r="E156" s="76" t="n"/>
+      <c r="E156" s="90" t="n"/>
+      <c r="F156" s="76" t="n"/>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="19" t="n"/>
       <c r="B157" s="20" t="n"/>
       <c r="C157" s="76" t="n"/>
       <c r="D157" s="68" t="n"/>
-      <c r="E157" s="76" t="n"/>
+      <c r="E157" s="90" t="n"/>
+      <c r="F157" s="76" t="n"/>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="19" t="n"/>
       <c r="B158" s="20" t="n"/>
       <c r="C158" s="76" t="n"/>
       <c r="D158" s="68" t="n"/>
-      <c r="E158" s="76" t="n"/>
+      <c r="E158" s="90" t="n"/>
+      <c r="F158" s="76" t="n"/>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="19" t="n"/>
       <c r="B159" s="20" t="n"/>
       <c r="C159" s="76" t="n"/>
       <c r="D159" s="68" t="n"/>
-      <c r="E159" s="76" t="n"/>
+      <c r="E159" s="90" t="n"/>
+      <c r="F159" s="76" t="n"/>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="19" t="n"/>
       <c r="B160" s="20" t="n"/>
       <c r="C160" s="76" t="n"/>
       <c r="D160" s="68" t="n"/>
-      <c r="E160" s="76" t="n"/>
+      <c r="E160" s="90" t="n"/>
+      <c r="F160" s="76" t="n"/>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="19" t="n"/>
       <c r="B161" s="20" t="n"/>
       <c r="C161" s="76" t="n"/>
       <c r="D161" s="68" t="n"/>
-      <c r="E161" s="76" t="n"/>
+      <c r="E161" s="90" t="n"/>
+      <c r="F161" s="76" t="n"/>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="19" t="n"/>
       <c r="B162" s="20" t="n"/>
       <c r="C162" s="76" t="n"/>
       <c r="D162" s="68" t="n"/>
-      <c r="E162" s="76" t="n"/>
+      <c r="E162" s="90" t="n"/>
+      <c r="F162" s="76" t="n"/>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="19" t="n"/>
       <c r="B163" s="20" t="n"/>
       <c r="C163" s="76" t="n"/>
       <c r="D163" s="68" t="n"/>
-      <c r="E163" s="76" t="n"/>
+      <c r="E163" s="90" t="n"/>
+      <c r="F163" s="76" t="n"/>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="19" t="n"/>
       <c r="B164" s="20" t="n"/>
       <c r="C164" s="76" t="n"/>
       <c r="D164" s="68" t="n"/>
-      <c r="E164" s="76" t="n"/>
+      <c r="E164" s="90" t="n"/>
+      <c r="F164" s="76" t="n"/>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="19" t="n"/>
       <c r="B165" s="20" t="n"/>
       <c r="C165" s="76" t="n"/>
       <c r="D165" s="68" t="n"/>
-      <c r="E165" s="76" t="n"/>
+      <c r="E165" s="90" t="n"/>
+      <c r="F165" s="76" t="n"/>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="19" t="n"/>
       <c r="B166" s="20" t="n"/>
       <c r="C166" s="76" t="n"/>
       <c r="D166" s="68" t="n"/>
-      <c r="E166" s="76" t="n"/>
+      <c r="E166" s="90" t="n"/>
+      <c r="F166" s="76" t="n"/>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="19" t="n"/>
       <c r="B167" s="20" t="n"/>
       <c r="C167" s="76" t="n"/>
       <c r="D167" s="68" t="n"/>
-      <c r="E167" s="76" t="n"/>
+      <c r="E167" s="90" t="n"/>
+      <c r="F167" s="76" t="n"/>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="19" t="n"/>
       <c r="B168" s="20" t="n"/>
       <c r="C168" s="76" t="n"/>
       <c r="D168" s="68" t="n"/>
-      <c r="E168" s="76" t="n"/>
+      <c r="E168" s="90" t="n"/>
+      <c r="F168" s="76" t="n"/>
     </row>
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="19" t="n"/>
       <c r="B169" s="20" t="n"/>
       <c r="C169" s="76" t="n"/>
       <c r="D169" s="68" t="n"/>
-      <c r="E169" s="76" t="n"/>
+      <c r="E169" s="90" t="n"/>
+      <c r="F169" s="76" t="n"/>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="19" t="n"/>
       <c r="B170" s="20" t="n"/>
       <c r="C170" s="76" t="n"/>
       <c r="D170" s="68" t="n"/>
-      <c r="E170" s="76" t="n"/>
+      <c r="E170" s="90" t="n"/>
+      <c r="F170" s="76" t="n"/>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="19" t="n"/>
       <c r="B171" s="20" t="n"/>
       <c r="C171" s="76" t="n"/>
       <c r="D171" s="68" t="n"/>
-      <c r="E171" s="76" t="n"/>
+      <c r="E171" s="90" t="n"/>
+      <c r="F171" s="76" t="n"/>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="19" t="n"/>
       <c r="B172" s="20" t="n"/>
       <c r="C172" s="76" t="n"/>
       <c r="D172" s="68" t="n"/>
-      <c r="E172" s="76" t="n"/>
+      <c r="E172" s="90" t="n"/>
+      <c r="F172" s="76" t="n"/>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="19" t="n"/>
       <c r="B173" s="20" t="n"/>
       <c r="C173" s="76" t="n"/>
       <c r="D173" s="68" t="n"/>
-      <c r="E173" s="76" t="n"/>
+      <c r="E173" s="90" t="n"/>
+      <c r="F173" s="76" t="n"/>
     </row>
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="19" t="n"/>
       <c r="B174" s="20" t="n"/>
       <c r="C174" s="76" t="n"/>
       <c r="D174" s="68" t="n"/>
-      <c r="E174" s="76" t="n"/>
+      <c r="E174" s="90" t="n"/>
+      <c r="F174" s="76" t="n"/>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="19" t="n"/>
       <c r="B175" s="20" t="n"/>
       <c r="C175" s="76" t="n"/>
       <c r="D175" s="68" t="n"/>
-      <c r="E175" s="76" t="n"/>
+      <c r="E175" s="90" t="n"/>
+      <c r="F175" s="76" t="n"/>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="19" t="n"/>
       <c r="B176" s="20" t="n"/>
       <c r="C176" s="76" t="n"/>
       <c r="D176" s="68" t="n"/>
-      <c r="E176" s="76" t="n"/>
+      <c r="E176" s="90" t="n"/>
+      <c r="F176" s="76" t="n"/>
     </row>
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="19" t="n"/>
       <c r="B177" s="20" t="n"/>
       <c r="C177" s="76" t="n"/>
       <c r="D177" s="68" t="n"/>
-      <c r="E177" s="76" t="n"/>
+      <c r="E177" s="90" t="n"/>
+      <c r="F177" s="76" t="n"/>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="19" t="n"/>
       <c r="B178" s="20" t="n"/>
       <c r="C178" s="76" t="n"/>
       <c r="D178" s="68" t="n"/>
-      <c r="E178" s="76" t="n"/>
+      <c r="E178" s="90" t="n"/>
+      <c r="F178" s="76" t="n"/>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="19" t="n"/>
       <c r="B179" s="20" t="n"/>
       <c r="C179" s="76" t="n"/>
       <c r="D179" s="68" t="n"/>
-      <c r="E179" s="76" t="n"/>
+      <c r="E179" s="90" t="n"/>
+      <c r="F179" s="76" t="n"/>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="19" t="n"/>
       <c r="B180" s="20" t="n"/>
       <c r="C180" s="76" t="n"/>
       <c r="D180" s="68" t="n"/>
-      <c r="E180" s="76" t="n"/>
+      <c r="E180" s="90" t="n"/>
+      <c r="F180" s="76" t="n"/>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="19" t="n"/>
       <c r="B181" s="20" t="n"/>
       <c r="C181" s="76" t="n"/>
       <c r="D181" s="68" t="n"/>
-      <c r="E181" s="76" t="n"/>
+      <c r="E181" s="90" t="n"/>
+      <c r="F181" s="76" t="n"/>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="19" t="n"/>
       <c r="B182" s="20" t="n"/>
       <c r="C182" s="76" t="n"/>
       <c r="D182" s="68" t="n"/>
-      <c r="E182" s="76" t="n"/>
+      <c r="E182" s="90" t="n"/>
+      <c r="F182" s="76" t="n"/>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="19" t="n"/>
       <c r="B183" s="20" t="n"/>
       <c r="C183" s="76" t="n"/>
       <c r="D183" s="68" t="n"/>
-      <c r="E183" s="76" t="n"/>
+      <c r="E183" s="90" t="n"/>
+      <c r="F183" s="76" t="n"/>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="19" t="n"/>
       <c r="B184" s="20" t="n"/>
       <c r="C184" s="76" t="n"/>
       <c r="D184" s="68" t="n"/>
-      <c r="E184" s="76" t="n"/>
+      <c r="E184" s="90" t="n"/>
+      <c r="F184" s="76" t="n"/>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="19" t="n"/>
       <c r="B185" s="20" t="n"/>
       <c r="C185" s="76" t="n"/>
       <c r="D185" s="68" t="n"/>
-      <c r="E185" s="76" t="n"/>
+      <c r="E185" s="90" t="n"/>
+      <c r="F185" s="76" t="n"/>
     </row>
     <row r="186" ht="20" customHeight="1">
       <c r="A186" s="19" t="n"/>
       <c r="B186" s="20" t="n"/>
       <c r="C186" s="76" t="n"/>
       <c r="D186" s="68" t="n"/>
-      <c r="E186" s="76" t="n"/>
+      <c r="E186" s="90" t="n"/>
+      <c r="F186" s="76" t="n"/>
     </row>
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="19" t="n"/>
       <c r="B187" s="20" t="n"/>
       <c r="C187" s="76" t="n"/>
       <c r="D187" s="68" t="n"/>
-      <c r="E187" s="76" t="n"/>
+      <c r="E187" s="90" t="n"/>
+      <c r="F187" s="76" t="n"/>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="19" t="n"/>
       <c r="B188" s="20" t="n"/>
       <c r="C188" s="76" t="n"/>
       <c r="D188" s="68" t="n"/>
-      <c r="E188" s="76" t="n"/>
+      <c r="E188" s="90" t="n"/>
+      <c r="F188" s="76" t="n"/>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="19" t="n"/>
       <c r="B189" s="20" t="n"/>
       <c r="C189" s="76" t="n"/>
       <c r="D189" s="68" t="n"/>
-      <c r="E189" s="76" t="n"/>
+      <c r="E189" s="90" t="n"/>
+      <c r="F189" s="76" t="n"/>
     </row>
     <row r="190" ht="20" customHeight="1">
       <c r="A190" s="19" t="n"/>
       <c r="B190" s="20" t="n"/>
       <c r="C190" s="76" t="n"/>
       <c r="D190" s="68" t="n"/>
-      <c r="E190" s="76" t="n"/>
+      <c r="E190" s="90" t="n"/>
+      <c r="F190" s="76" t="n"/>
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="19" t="n"/>
       <c r="B191" s="20" t="n"/>
       <c r="C191" s="76" t="n"/>
       <c r="D191" s="68" t="n"/>
-      <c r="E191" s="76" t="n"/>
+      <c r="E191" s="90" t="n"/>
+      <c r="F191" s="76" t="n"/>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="19" t="n"/>
       <c r="B192" s="20" t="n"/>
       <c r="C192" s="76" t="n"/>
       <c r="D192" s="68" t="n"/>
-      <c r="E192" s="76" t="n"/>
+      <c r="E192" s="90" t="n"/>
+      <c r="F192" s="76" t="n"/>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="19" t="n"/>
       <c r="B193" s="20" t="n"/>
       <c r="C193" s="76" t="n"/>
       <c r="D193" s="68" t="n"/>
-      <c r="E193" s="76" t="n"/>
+      <c r="E193" s="90" t="n"/>
+      <c r="F193" s="76" t="n"/>
     </row>
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="19" t="n"/>
       <c r="B194" s="20" t="n"/>
       <c r="C194" s="76" t="n"/>
       <c r="D194" s="68" t="n"/>
-      <c r="E194" s="76" t="n"/>
+      <c r="E194" s="90" t="n"/>
+      <c r="F194" s="76" t="n"/>
     </row>
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="19" t="n"/>
       <c r="B195" s="20" t="n"/>
       <c r="C195" s="76" t="n"/>
       <c r="D195" s="68" t="n"/>
-      <c r="E195" s="76" t="n"/>
+      <c r="E195" s="90" t="n"/>
+      <c r="F195" s="76" t="n"/>
     </row>
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="19" t="n"/>
       <c r="B196" s="20" t="n"/>
       <c r="C196" s="76" t="n"/>
       <c r="D196" s="68" t="n"/>
-      <c r="E196" s="76" t="n"/>
+      <c r="E196" s="90" t="n"/>
+      <c r="F196" s="76" t="n"/>
     </row>
     <row r="197" ht="20" customHeight="1">
       <c r="A197" s="19" t="n"/>
       <c r="B197" s="20" t="n"/>
       <c r="C197" s="76" t="n"/>
       <c r="D197" s="68" t="n"/>
-      <c r="E197" s="76" t="n"/>
+      <c r="E197" s="90" t="n"/>
+      <c r="F197" s="76" t="n"/>
     </row>
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="19" t="n"/>
       <c r="B198" s="20" t="n"/>
       <c r="C198" s="76" t="n"/>
       <c r="D198" s="68" t="n"/>
-      <c r="E198" s="76" t="n"/>
+      <c r="E198" s="90" t="n"/>
+      <c r="F198" s="76" t="n"/>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="19" t="n"/>
       <c r="B199" s="20" t="n"/>
       <c r="C199" s="76" t="n"/>
       <c r="D199" s="68" t="n"/>
-      <c r="E199" s="76" t="n"/>
+      <c r="E199" s="90" t="n"/>
+      <c r="F199" s="76" t="n"/>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="19" t="n"/>
       <c r="B200" s="20" t="n"/>
       <c r="C200" s="76" t="n"/>
       <c r="D200" s="68" t="n"/>
-      <c r="E200" s="76" t="n"/>
+      <c r="E200" s="90" t="n"/>
+      <c r="F200" s="76" t="n"/>
     </row>
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="19" t="n"/>
       <c r="B201" s="20" t="n"/>
       <c r="C201" s="76" t="n"/>
       <c r="D201" s="68" t="n"/>
-      <c r="E201" s="76" t="n"/>
+      <c r="E201" s="90" t="n"/>
+      <c r="F201" s="76" t="n"/>
     </row>
     <row r="202" ht="20" customHeight="1">
       <c r="A202" s="19" t="n"/>
       <c r="B202" s="20" t="n"/>
       <c r="C202" s="76" t="n"/>
       <c r="D202" s="68" t="n"/>
-      <c r="E202" s="76" t="n"/>
+      <c r="E202" s="90" t="n"/>
+      <c r="F202" s="76" t="n"/>
     </row>
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="19" t="n"/>
       <c r="B203" s="20" t="n"/>
       <c r="C203" s="76" t="n"/>
       <c r="D203" s="68" t="n"/>
-      <c r="E203" s="76" t="n"/>
+      <c r="E203" s="90" t="n"/>
+      <c r="F203" s="76" t="n"/>
     </row>
     <row r="204" ht="20" customHeight="1">
       <c r="A204" s="19" t="n"/>
       <c r="B204" s="20" t="n"/>
       <c r="C204" s="76" t="n"/>
       <c r="D204" s="68" t="n"/>
-      <c r="E204" s="76" t="n"/>
+      <c r="E204" s="90" t="n"/>
+      <c r="F204" s="76" t="n"/>
     </row>
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="19" t="n"/>
       <c r="B205" s="20" t="n"/>
       <c r="C205" s="76" t="n"/>
       <c r="D205" s="68" t="n"/>
-      <c r="E205" s="76" t="n"/>
+      <c r="E205" s="90" t="n"/>
+      <c r="F205" s="76" t="n"/>
     </row>
     <row r="206" ht="20" customHeight="1">
       <c r="A206" s="19" t="n"/>
       <c r="B206" s="20" t="n"/>
       <c r="C206" s="76" t="n"/>
       <c r="D206" s="68" t="n"/>
-      <c r="E206" s="76" t="n"/>
+      <c r="E206" s="90" t="n"/>
+      <c r="F206" s="76" t="n"/>
     </row>
     <row r="207" ht="20" customHeight="1">
       <c r="A207" s="19" t="n"/>
       <c r="B207" s="20" t="n"/>
       <c r="C207" s="76" t="n"/>
       <c r="D207" s="68" t="n"/>
-      <c r="E207" s="76" t="n"/>
+      <c r="E207" s="90" t="n"/>
+      <c r="F207" s="76" t="n"/>
     </row>
     <row r="208" ht="20" customHeight="1">
       <c r="A208" s="19" t="n"/>
       <c r="B208" s="20" t="n"/>
       <c r="C208" s="76" t="n"/>
       <c r="D208" s="68" t="n"/>
-      <c r="E208" s="76" t="n"/>
+      <c r="E208" s="90" t="n"/>
+      <c r="F208" s="76" t="n"/>
     </row>
     <row r="209" ht="20" customHeight="1">
       <c r="A209" s="19" t="n"/>
       <c r="B209" s="20" t="n"/>
       <c r="C209" s="76" t="n"/>
       <c r="D209" s="68" t="n"/>
-      <c r="E209" s="76" t="n"/>
+      <c r="E209" s="90" t="n"/>
+      <c r="F209" s="76" t="n"/>
     </row>
     <row r="210" ht="20" customHeight="1">
       <c r="A210" s="19" t="n"/>
       <c r="B210" s="20" t="n"/>
       <c r="C210" s="76" t="n"/>
       <c r="D210" s="68" t="n"/>
-      <c r="E210" s="76" t="n"/>
+      <c r="E210" s="90" t="n"/>
+      <c r="F210" s="76" t="n"/>
     </row>
     <row r="211" ht="20" customHeight="1">
       <c r="A211" s="19" t="n"/>
       <c r="B211" s="20" t="n"/>
       <c r="C211" s="76" t="n"/>
       <c r="D211" s="68" t="n"/>
-      <c r="E211" s="76" t="n"/>
+      <c r="E211" s="90" t="n"/>
+      <c r="F211" s="76" t="n"/>
     </row>
     <row r="212" ht="20" customHeight="1">
       <c r="A212" s="19" t="n"/>
       <c r="B212" s="20" t="n"/>
       <c r="C212" s="76" t="n"/>
       <c r="D212" s="68" t="n"/>
-      <c r="E212" s="76" t="n"/>
+      <c r="E212" s="90" t="n"/>
+      <c r="F212" s="76" t="n"/>
     </row>
     <row r="213" ht="20" customHeight="1">
       <c r="A213" s="19" t="n"/>
       <c r="B213" s="20" t="n"/>
       <c r="C213" s="76" t="n"/>
       <c r="D213" s="68" t="n"/>
-      <c r="E213" s="76" t="n"/>
+      <c r="E213" s="90" t="n"/>
+      <c r="F213" s="76" t="n"/>
     </row>
     <row r="214" ht="20" customHeight="1">
       <c r="A214" s="19" t="n"/>
       <c r="B214" s="20" t="n"/>
       <c r="C214" s="76" t="n"/>
       <c r="D214" s="68" t="n"/>
-      <c r="E214" s="76" t="n"/>
+      <c r="E214" s="90" t="n"/>
+      <c r="F214" s="76" t="n"/>
     </row>
     <row r="215" ht="20" customHeight="1">
       <c r="A215" s="19" t="n"/>
       <c r="B215" s="20" t="n"/>
       <c r="C215" s="76" t="n"/>
       <c r="D215" s="68" t="n"/>
-      <c r="E215" s="76" t="n"/>
+      <c r="E215" s="90" t="n"/>
+      <c r="F215" s="76" t="n"/>
     </row>
     <row r="216" ht="20" customHeight="1">
       <c r="A216" s="19" t="n"/>
       <c r="B216" s="20" t="n"/>
       <c r="C216" s="76" t="n"/>
       <c r="D216" s="68" t="n"/>
-      <c r="E216" s="76" t="n"/>
+      <c r="E216" s="90" t="n"/>
+      <c r="F216" s="76" t="n"/>
     </row>
     <row r="217" ht="20" customHeight="1">
       <c r="A217" s="19" t="n"/>
       <c r="B217" s="20" t="n"/>
       <c r="C217" s="76" t="n"/>
       <c r="D217" s="68" t="n"/>
-      <c r="E217" s="76" t="n"/>
+      <c r="E217" s="90" t="n"/>
+      <c r="F217" s="76" t="n"/>
     </row>
     <row r="218" ht="20" customHeight="1">
       <c r="A218" s="19" t="n"/>
       <c r="B218" s="20" t="n"/>
       <c r="C218" s="76" t="n"/>
       <c r="D218" s="68" t="n"/>
-      <c r="E218" s="76" t="n"/>
+      <c r="E218" s="90" t="n"/>
+      <c r="F218" s="76" t="n"/>
     </row>
     <row r="219" ht="20" customHeight="1">
       <c r="A219" s="19" t="n"/>
       <c r="B219" s="20" t="n"/>
       <c r="C219" s="76" t="n"/>
       <c r="D219" s="68" t="n"/>
-      <c r="E219" s="76" t="n"/>
+      <c r="E219" s="90" t="n"/>
+      <c r="F219" s="76" t="n"/>
     </row>
     <row r="220" ht="20" customHeight="1">
       <c r="A220" s="19" t="n"/>
       <c r="B220" s="20" t="n"/>
       <c r="C220" s="76" t="n"/>
       <c r="D220" s="68" t="n"/>
-      <c r="E220" s="76" t="n"/>
+      <c r="E220" s="90" t="n"/>
+      <c r="F220" s="76" t="n"/>
     </row>
     <row r="221" ht="20" customHeight="1">
       <c r="A221" s="19" t="n"/>
       <c r="B221" s="20" t="n"/>
       <c r="C221" s="76" t="n"/>
       <c r="D221" s="68" t="n"/>
-      <c r="E221" s="76" t="n"/>
+      <c r="E221" s="90" t="n"/>
+      <c r="F221" s="76" t="n"/>
     </row>
     <row r="222" ht="20" customHeight="1">
       <c r="A222" s="19" t="n"/>
       <c r="B222" s="20" t="n"/>
       <c r="C222" s="76" t="n"/>
       <c r="D222" s="68" t="n"/>
-      <c r="E222" s="76" t="n"/>
+      <c r="E222" s="90" t="n"/>
+      <c r="F222" s="76" t="n"/>
     </row>
     <row r="223" ht="20" customHeight="1">
       <c r="A223" s="19" t="n"/>
       <c r="B223" s="20" t="n"/>
       <c r="C223" s="76" t="n"/>
       <c r="D223" s="68" t="n"/>
-      <c r="E223" s="76" t="n"/>
+      <c r="E223" s="90" t="n"/>
+      <c r="F223" s="76" t="n"/>
     </row>
     <row r="224" ht="20" customHeight="1">
       <c r="A224" s="19" t="n"/>
       <c r="B224" s="20" t="n"/>
       <c r="C224" s="76" t="n"/>
       <c r="D224" s="68" t="n"/>
-      <c r="E224" s="76" t="n"/>
+      <c r="E224" s="90" t="n"/>
+      <c r="F224" s="76" t="n"/>
     </row>
     <row r="225" ht="20" customHeight="1">
       <c r="A225" s="19" t="n"/>
       <c r="B225" s="20" t="n"/>
       <c r="C225" s="76" t="n"/>
       <c r="D225" s="68" t="n"/>
-      <c r="E225" s="76" t="n"/>
+      <c r="E225" s="90" t="n"/>
+      <c r="F225" s="76" t="n"/>
     </row>
     <row r="226" ht="20" customHeight="1">
       <c r="A226" s="19" t="n"/>
       <c r="B226" s="20" t="n"/>
       <c r="C226" s="76" t="n"/>
       <c r="D226" s="68" t="n"/>
-      <c r="E226" s="76" t="n"/>
+      <c r="E226" s="90" t="n"/>
+      <c r="F226" s="76" t="n"/>
     </row>
     <row r="227" ht="20" customHeight="1">
       <c r="A227" s="19" t="n"/>
       <c r="B227" s="20" t="n"/>
       <c r="C227" s="76" t="n"/>
       <c r="D227" s="68" t="n"/>
-      <c r="E227" s="76" t="n"/>
+      <c r="E227" s="90" t="n"/>
+      <c r="F227" s="76" t="n"/>
     </row>
     <row r="228" ht="20" customHeight="1">
       <c r="A228" s="19" t="n"/>
       <c r="B228" s="20" t="n"/>
       <c r="C228" s="76" t="n"/>
       <c r="D228" s="68" t="n"/>
-      <c r="E228" s="76" t="n"/>
+      <c r="E228" s="90" t="n"/>
+      <c r="F228" s="76" t="n"/>
     </row>
     <row r="229" ht="20" customHeight="1">
       <c r="A229" s="19" t="n"/>
       <c r="B229" s="20" t="n"/>
       <c r="C229" s="76" t="n"/>
       <c r="D229" s="68" t="n"/>
-      <c r="E229" s="76" t="n"/>
+      <c r="E229" s="90" t="n"/>
+      <c r="F229" s="76" t="n"/>
     </row>
     <row r="230" ht="20" customHeight="1">
       <c r="A230" s="19" t="n"/>
       <c r="B230" s="20" t="n"/>
       <c r="C230" s="76" t="n"/>
       <c r="D230" s="68" t="n"/>
-      <c r="E230" s="76" t="n"/>
+      <c r="E230" s="90" t="n"/>
+      <c r="F230" s="76" t="n"/>
     </row>
     <row r="231" ht="20" customHeight="1">
       <c r="A231" s="19" t="n"/>
       <c r="B231" s="20" t="n"/>
       <c r="C231" s="76" t="n"/>
       <c r="D231" s="68" t="n"/>
-      <c r="E231" s="76" t="n"/>
+      <c r="E231" s="90" t="n"/>
+      <c r="F231" s="76" t="n"/>
     </row>
     <row r="232" ht="20" customHeight="1">
       <c r="A232" s="19" t="n"/>
       <c r="B232" s="20" t="n"/>
       <c r="C232" s="76" t="n"/>
       <c r="D232" s="68" t="n"/>
-      <c r="E232" s="76" t="n"/>
+      <c r="E232" s="90" t="n"/>
+      <c r="F232" s="76" t="n"/>
     </row>
     <row r="233" ht="20" customHeight="1">
       <c r="A233" s="19" t="n"/>
       <c r="B233" s="20" t="n"/>
       <c r="C233" s="76" t="n"/>
       <c r="D233" s="68" t="n"/>
-      <c r="E233" s="76" t="n"/>
+      <c r="E233" s="90" t="n"/>
+      <c r="F233" s="76" t="n"/>
     </row>
     <row r="234" ht="20" customHeight="1">
       <c r="A234" s="19" t="n"/>
       <c r="B234" s="20" t="n"/>
       <c r="C234" s="76" t="n"/>
       <c r="D234" s="68" t="n"/>
-      <c r="E234" s="76" t="n"/>
+      <c r="E234" s="90" t="n"/>
+      <c r="F234" s="76" t="n"/>
     </row>
     <row r="235" ht="20" customHeight="1">
       <c r="A235" s="19" t="n"/>
       <c r="B235" s="20" t="n"/>
       <c r="C235" s="76" t="n"/>
       <c r="D235" s="68" t="n"/>
-      <c r="E235" s="76" t="n"/>
+      <c r="E235" s="90" t="n"/>
+      <c r="F235" s="76" t="n"/>
     </row>
     <row r="236" ht="20" customHeight="1">
       <c r="A236" s="19" t="n"/>
       <c r="B236" s="20" t="n"/>
       <c r="C236" s="76" t="n"/>
       <c r="D236" s="68" t="n"/>
-      <c r="E236" s="76" t="n"/>
+      <c r="E236" s="90" t="n"/>
+      <c r="F236" s="76" t="n"/>
     </row>
     <row r="237" ht="20" customHeight="1">
       <c r="A237" s="19" t="n"/>
       <c r="B237" s="20" t="n"/>
       <c r="C237" s="76" t="n"/>
       <c r="D237" s="68" t="n"/>
-      <c r="E237" s="76" t="n"/>
+      <c r="E237" s="90" t="n"/>
+      <c r="F237" s="76" t="n"/>
     </row>
     <row r="238" ht="20" customHeight="1">
       <c r="A238" s="19" t="n"/>
       <c r="B238" s="20" t="n"/>
       <c r="C238" s="76" t="n"/>
       <c r="D238" s="68" t="n"/>
-      <c r="E238" s="76" t="n"/>
+      <c r="E238" s="90" t="n"/>
+      <c r="F238" s="76" t="n"/>
     </row>
     <row r="239" ht="20" customHeight="1">
       <c r="A239" s="19" t="n"/>
       <c r="B239" s="20" t="n"/>
       <c r="C239" s="76" t="n"/>
       <c r="D239" s="68" t="n"/>
-      <c r="E239" s="76" t="n"/>
+      <c r="E239" s="90" t="n"/>
+      <c r="F239" s="76" t="n"/>
     </row>
     <row r="240" ht="20" customHeight="1">
       <c r="A240" s="19" t="n"/>
       <c r="B240" s="20" t="n"/>
       <c r="C240" s="76" t="n"/>
       <c r="D240" s="68" t="n"/>
-      <c r="E240" s="76" t="n"/>
+      <c r="E240" s="90" t="n"/>
+      <c r="F240" s="76" t="n"/>
     </row>
     <row r="241" ht="20" customHeight="1">
       <c r="A241" s="19" t="n"/>
       <c r="B241" s="20" t="n"/>
       <c r="C241" s="76" t="n"/>
       <c r="D241" s="68" t="n"/>
-      <c r="E241" s="76" t="n"/>
+      <c r="E241" s="90" t="n"/>
+      <c r="F241" s="76" t="n"/>
     </row>
     <row r="242" ht="20" customHeight="1">
       <c r="A242" s="19" t="n"/>
       <c r="B242" s="20" t="n"/>
       <c r="C242" s="76" t="n"/>
       <c r="D242" s="68" t="n"/>
-      <c r="E242" s="76" t="n"/>
+      <c r="E242" s="90" t="n"/>
+      <c r="F242" s="76" t="n"/>
     </row>
     <row r="243" ht="20" customHeight="1">
       <c r="A243" s="19" t="n"/>
       <c r="B243" s="20" t="n"/>
       <c r="C243" s="76" t="n"/>
       <c r="D243" s="68" t="n"/>
-      <c r="E243" s="76" t="n"/>
+      <c r="E243" s="90" t="n"/>
+      <c r="F243" s="76" t="n"/>
     </row>
     <row r="244" ht="20" customHeight="1">
       <c r="A244" s="19" t="n"/>
       <c r="B244" s="20" t="n"/>
       <c r="C244" s="76" t="n"/>
       <c r="D244" s="68" t="n"/>
-      <c r="E244" s="76" t="n"/>
+      <c r="E244" s="90" t="n"/>
+      <c r="F244" s="76" t="n"/>
     </row>
     <row r="245" ht="20" customHeight="1">
       <c r="A245" s="19" t="n"/>
       <c r="B245" s="20" t="n"/>
       <c r="C245" s="76" t="n"/>
       <c r="D245" s="68" t="n"/>
-      <c r="E245" s="76" t="n"/>
+      <c r="E245" s="90" t="n"/>
+      <c r="F245" s="76" t="n"/>
     </row>
     <row r="246" ht="20" customHeight="1">
       <c r="A246" s="19" t="n"/>
       <c r="B246" s="20" t="n"/>
       <c r="C246" s="76" t="n"/>
       <c r="D246" s="68" t="n"/>
-      <c r="E246" s="76" t="n"/>
+      <c r="E246" s="90" t="n"/>
+      <c r="F246" s="76" t="n"/>
     </row>
     <row r="247" ht="20" customHeight="1">
       <c r="A247" s="19" t="n"/>
       <c r="B247" s="20" t="n"/>
       <c r="C247" s="76" t="n"/>
       <c r="D247" s="68" t="n"/>
-      <c r="E247" s="76" t="n"/>
+      <c r="E247" s="90" t="n"/>
+      <c r="F247" s="76" t="n"/>
     </row>
     <row r="248" ht="20" customHeight="1">
       <c r="A248" s="19" t="n"/>
       <c r="B248" s="20" t="n"/>
       <c r="C248" s="76" t="n"/>
       <c r="D248" s="68" t="n"/>
-      <c r="E248" s="76" t="n"/>
+      <c r="E248" s="90" t="n"/>
+      <c r="F248" s="76" t="n"/>
     </row>
     <row r="249" ht="20" customHeight="1">
       <c r="A249" s="19" t="n"/>
       <c r="B249" s="20" t="n"/>
       <c r="C249" s="76" t="n"/>
       <c r="D249" s="68" t="n"/>
-      <c r="E249" s="76" t="n"/>
+      <c r="E249" s="90" t="n"/>
+      <c r="F249" s="76" t="n"/>
     </row>
     <row r="250" ht="20" customHeight="1">
       <c r="A250" s="19" t="n"/>
       <c r="B250" s="20" t="n"/>
       <c r="C250" s="76" t="n"/>
       <c r="D250" s="68" t="n"/>
-      <c r="E250" s="76" t="n"/>
+      <c r="E250" s="90" t="n"/>
+      <c r="F250" s="76" t="n"/>
     </row>
     <row r="251" ht="20" customHeight="1">
       <c r="A251" s="19" t="n"/>
       <c r="B251" s="20" t="n"/>
       <c r="C251" s="76" t="n"/>
       <c r="D251" s="68" t="n"/>
-      <c r="E251" s="76" t="n"/>
+      <c r="E251" s="90" t="n"/>
+      <c r="F251" s="76" t="n"/>
     </row>
     <row r="252" ht="20" customHeight="1">
       <c r="A252" s="19" t="n"/>
       <c r="B252" s="20" t="n"/>
       <c r="C252" s="76" t="n"/>
       <c r="D252" s="68" t="n"/>
-      <c r="E252" s="76" t="n"/>
+      <c r="E252" s="90" t="n"/>
+      <c r="F252" s="76" t="n"/>
     </row>
     <row r="254" ht="28" customHeight="1">
       <c r="A254" s="24" t="inlineStr">
         <is>
-          <t>זו רשימת ההיצע לגיליון «שיבוץ». מותר ורצוי להוסיף, למחוק ולתקן — הרשימה הנגללת והקטגוריה האוטומטית מתעדכנות לבד. משימות ניקיון מופיעות בנפרד לכל מרחב, כדי לבחור בכל שבת אילו מרחבים מנקים ומתי. עמודת «עוגן» היא ברירת המחדל לשיוך המשימה בלו"ז הצל.</t>
+          <t>זו רשימת ההיצע לגיליון «שיבוץ». מותר ורצוי להוסיף, למחוק ולתקן — הרשימה הנגללת והקטגוריה האוטומטית מתעדכנות לבד. משימות ניקיון מופיעות בנפרד לכל מרחב, כדי לבחור בכל שבת אילו מרחבים מנקים ומתי. «שעה» ו«עוגן» הן ברירות המחדל שנכתבות לשיבוץ ומשם ללו"ז הצל.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A254:D254"/>
+    <mergeCell ref="A254:F254"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="A3:A252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -18528,7 +18601,7 @@
     <dataValidation sqref="C3:C252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"שישי,שבת,מוצאי שבת,חמישי,משתנה"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"חמישי — הכנות,שישי — ארוחת בוקר,שישי — הכנות ועבודה,שישי — ארוחת צהריים,קבלת שבת ישראלית,כניסת שבת,קבלת שבת וערבית,סעודת שבת,טיש עם איש צוות,קידוש,חבורות חניכים,ארוחת צהריים,חבורה עם איש צוות,סעודה שלישית,הבדלה,ניקיונות וארגון הקמפוס,כריכה לכריכה"</formula1>
     </dataValidation>
   </dataValidations>
@@ -24126,7 +24199,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="93" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>לוח שבתות — זמני ירושלים</t>
         </is>
@@ -24160,7 +24233,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="94" t="n">
+      <c r="A3" s="95" t="n">
         <v>46269</v>
       </c>
       <c r="B3" s="20" t="inlineStr">
@@ -24174,14 +24247,14 @@
       <c r="D3" s="82" t="n">
         <v>0.81875</v>
       </c>
-      <c r="E3" s="95" t="inlineStr">
+      <c r="E3" s="96" t="inlineStr">
         <is>
           <t>הזמנים מחושבים לירושלים (כניסה 40 דק' לפני השקיעה, צאה 40 דק' אחריה) ומדויקים לדקה-שתיים. אם הלוח שלך אומר אחרת — תקנו את השורה. הצבע הצהוב מסמן שדה שמותר לשנות.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="94" t="n">
+      <c r="A4" s="95" t="n">
         <v>46276</v>
       </c>
       <c r="B4" s="20" t="inlineStr">
@@ -24197,7 +24270,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="94" t="n">
+      <c r="A5" s="95" t="n">
         <v>46283</v>
       </c>
       <c r="B5" s="20" t="inlineStr">
@@ -24213,7 +24286,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="94" t="n">
+      <c r="A6" s="95" t="n">
         <v>46290</v>
       </c>
       <c r="B6" s="20" t="inlineStr">
@@ -24229,7 +24302,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="94" t="n">
+      <c r="A7" s="95" t="n">
         <v>46297</v>
       </c>
       <c r="B7" s="20" t="inlineStr">
@@ -24245,7 +24318,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="94" t="n">
+      <c r="A8" s="95" t="n">
         <v>46304</v>
       </c>
       <c r="B8" s="20" t="inlineStr">
@@ -24261,7 +24334,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="94" t="n">
+      <c r="A9" s="95" t="n">
         <v>46311</v>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -24277,7 +24350,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="94" t="n">
+      <c r="A10" s="95" t="n">
         <v>46318</v>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -24293,7 +24366,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="94" t="n">
+      <c r="A11" s="95" t="n">
         <v>46325</v>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -24309,7 +24382,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="94" t="n">
+      <c r="A12" s="95" t="n">
         <v>46332</v>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -24325,7 +24398,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="94" t="n">
+      <c r="A13" s="95" t="n">
         <v>46339</v>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -24341,7 +24414,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="94" t="n">
+      <c r="A14" s="95" t="n">
         <v>46346</v>
       </c>
       <c r="B14" s="20" t="inlineStr">
@@ -24357,7 +24430,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="94" t="n">
+      <c r="A15" s="95" t="n">
         <v>46353</v>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -24373,7 +24446,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="94" t="n">
+      <c r="A16" s="95" t="n">
         <v>46360</v>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -24389,7 +24462,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="94" t="n">
+      <c r="A17" s="95" t="n">
         <v>46367</v>
       </c>
       <c r="B17" s="20" t="inlineStr">
@@ -24405,7 +24478,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="94" t="n">
+      <c r="A18" s="95" t="n">
         <v>46374</v>
       </c>
       <c r="B18" s="20" t="inlineStr">
@@ -24421,7 +24494,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="94" t="n">
+      <c r="A19" s="95" t="n">
         <v>46381</v>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -24437,7 +24510,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="94" t="n">
+      <c r="A20" s="95" t="n">
         <v>46388</v>
       </c>
       <c r="B20" s="20" t="inlineStr">
@@ -24453,7 +24526,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="94" t="n">
+      <c r="A21" s="95" t="n">
         <v>46395</v>
       </c>
       <c r="B21" s="20" t="inlineStr">
@@ -24469,7 +24542,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="94" t="n">
+      <c r="A22" s="95" t="n">
         <v>46402</v>
       </c>
       <c r="B22" s="20" t="inlineStr">
@@ -24485,7 +24558,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="94" t="n">
+      <c r="A23" s="95" t="n">
         <v>46409</v>
       </c>
       <c r="B23" s="20" t="inlineStr">
@@ -24501,7 +24574,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="94" t="n">
+      <c r="A24" s="95" t="n">
         <v>46416</v>
       </c>
       <c r="B24" s="20" t="inlineStr">
@@ -24517,7 +24590,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="94" t="n">
+      <c r="A25" s="95" t="n">
         <v>46423</v>
       </c>
       <c r="B25" s="20" t="inlineStr">
@@ -24533,7 +24606,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="94" t="n">
+      <c r="A26" s="95" t="n">
         <v>46430</v>
       </c>
       <c r="B26" s="20" t="inlineStr">
@@ -24549,7 +24622,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="94" t="n">
+      <c r="A27" s="95" t="n">
         <v>46437</v>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -24565,7 +24638,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="94" t="n">
+      <c r="A28" s="95" t="n">
         <v>46444</v>
       </c>
       <c r="B28" s="20" t="inlineStr">
@@ -24581,7 +24654,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="94" t="n">
+      <c r="A29" s="95" t="n">
         <v>46451</v>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -24597,7 +24670,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="94" t="n">
+      <c r="A30" s="95" t="n">
         <v>46458</v>
       </c>
       <c r="B30" s="20" t="inlineStr">
@@ -24613,7 +24686,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="94" t="n">
+      <c r="A31" s="95" t="n">
         <v>46465</v>
       </c>
       <c r="B31" s="20" t="inlineStr">
@@ -24629,7 +24702,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="94" t="n">
+      <c r="A32" s="95" t="n">
         <v>46472</v>
       </c>
       <c r="B32" s="20" t="inlineStr">
@@ -24645,7 +24718,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="94" t="n">
+      <c r="A33" s="95" t="n">
         <v>46479</v>
       </c>
       <c r="B33" s="20" t="inlineStr">
@@ -24661,7 +24734,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="94" t="n">
+      <c r="A34" s="95" t="n">
         <v>46486</v>
       </c>
       <c r="B34" s="20" t="inlineStr">
@@ -24677,7 +24750,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="94" t="n">
+      <c r="A35" s="95" t="n">
         <v>46493</v>
       </c>
       <c r="B35" s="20" t="inlineStr">
@@ -24693,7 +24766,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="94" t="n">
+      <c r="A36" s="95" t="n">
         <v>46500</v>
       </c>
       <c r="B36" s="20" t="inlineStr">
@@ -24709,7 +24782,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="94" t="n">
+      <c r="A37" s="95" t="n">
         <v>46507</v>
       </c>
       <c r="B37" s="20" t="inlineStr">
@@ -24725,7 +24798,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="94" t="n">
+      <c r="A38" s="95" t="n">
         <v>46514</v>
       </c>
       <c r="B38" s="20" t="inlineStr">
@@ -24741,7 +24814,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="94" t="n">
+      <c r="A39" s="95" t="n">
         <v>46521</v>
       </c>
       <c r="B39" s="20" t="inlineStr">
@@ -24757,7 +24830,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="94" t="n">
+      <c r="A40" s="95" t="n">
         <v>46528</v>
       </c>
       <c r="B40" s="20" t="inlineStr">
@@ -24773,7 +24846,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="94" t="n">
+      <c r="A41" s="95" t="n">
         <v>46535</v>
       </c>
       <c r="B41" s="20" t="inlineStr">
@@ -24789,7 +24862,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="94" t="n">
+      <c r="A42" s="95" t="n">
         <v>46542</v>
       </c>
       <c r="B42" s="20" t="inlineStr">
@@ -24805,7 +24878,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="94" t="n">
+      <c r="A43" s="95" t="n">
         <v>46549</v>
       </c>
       <c r="B43" s="20" t="inlineStr">
@@ -24821,7 +24894,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="94" t="n">
+      <c r="A44" s="95" t="n">
         <v>46556</v>
       </c>
       <c r="B44" s="20" t="inlineStr">
@@ -24837,7 +24910,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="94" t="n">
+      <c r="A45" s="95" t="n">
         <v>46563</v>
       </c>
       <c r="B45" s="20" t="inlineStr">
@@ -24853,7 +24926,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="94" t="n">
+      <c r="A46" s="95" t="n">
         <v>46570</v>
       </c>
       <c r="B46" s="20" t="inlineStr">
@@ -24869,7 +24942,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="94" t="n">
+      <c r="A47" s="95" t="n">
         <v>46577</v>
       </c>
       <c r="B47" s="20" t="inlineStr">
@@ -24885,7 +24958,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="94" t="n">
+      <c r="A48" s="95" t="n">
         <v>46584</v>
       </c>
       <c r="B48" s="20" t="inlineStr">
@@ -24901,7 +24974,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="94" t="n">
+      <c r="A49" s="95" t="n">
         <v>46591</v>
       </c>
       <c r="B49" s="20" t="inlineStr">
@@ -24917,7 +24990,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="94" t="n">
+      <c r="A50" s="95" t="n">
         <v>46598</v>
       </c>
       <c r="B50" s="20" t="inlineStr">
@@ -24933,7 +25006,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="94" t="n">
+      <c r="A51" s="95" t="n">
         <v>46605</v>
       </c>
       <c r="B51" s="20" t="inlineStr">
@@ -24949,7 +25022,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="94" t="n">
+      <c r="A52" s="95" t="n">
         <v>46612</v>
       </c>
       <c r="B52" s="20" t="inlineStr">
@@ -24965,7 +25038,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="94" t="n">
+      <c r="A53" s="95" t="n">
         <v>46619</v>
       </c>
       <c r="B53" s="20" t="inlineStr">
@@ -24981,7 +25054,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="94" t="n">
+      <c r="A54" s="95" t="n">
         <v>46626</v>
       </c>
       <c r="B54" s="20" t="inlineStr">
@@ -35639,9 +35712,9 @@
     <mergeCell ref="D84:E84"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D155:E155"/>
-    <mergeCell ref="D36:E36"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D36:E36"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="D158:E158"/>
     <mergeCell ref="D229:E229"/>
@@ -36724,8 +36797,8 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="96" t="n"/>
-      <c r="B6" s="96" t="n"/>
+      <c r="A6" s="97" t="n"/>
+      <c r="B6" s="97" t="n"/>
       <c r="C6" s="21">
         <f>$G6</f>
         <v/>
@@ -36738,8 +36811,8 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="96" t="n"/>
-      <c r="B7" s="96" t="n"/>
+      <c r="A7" s="97" t="n"/>
+      <c r="B7" s="97" t="n"/>
       <c r="C7" s="21">
         <f>$G7</f>
         <v/>
@@ -36752,8 +36825,8 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="96" t="n"/>
-      <c r="B8" s="96" t="n"/>
+      <c r="A8" s="97" t="n"/>
+      <c r="B8" s="97" t="n"/>
       <c r="C8" s="21">
         <f>$G8</f>
         <v/>
@@ -36766,8 +36839,8 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="97" t="n"/>
-      <c r="B9" s="97" t="n"/>
+      <c r="A9" s="98" t="n"/>
+      <c r="B9" s="98" t="n"/>
       <c r="C9" s="21">
         <f>$G9</f>
         <v/>
@@ -36798,8 +36871,8 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="96" t="n"/>
-      <c r="B11" s="96" t="n"/>
+      <c r="A11" s="97" t="n"/>
+      <c r="B11" s="97" t="n"/>
       <c r="C11" s="21">
         <f>$G11</f>
         <v/>
@@ -36812,8 +36885,8 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="96" t="n"/>
-      <c r="B12" s="96" t="n"/>
+      <c r="A12" s="97" t="n"/>
+      <c r="B12" s="97" t="n"/>
       <c r="C12" s="21">
         <f>$G12</f>
         <v/>
@@ -36826,8 +36899,8 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="96" t="n"/>
-      <c r="B13" s="96" t="n"/>
+      <c r="A13" s="97" t="n"/>
+      <c r="B13" s="97" t="n"/>
       <c r="C13" s="21">
         <f>$G13</f>
         <v/>
@@ -36840,8 +36913,8 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="97" t="n"/>
-      <c r="B14" s="97" t="n"/>
+      <c r="A14" s="98" t="n"/>
+      <c r="B14" s="98" t="n"/>
       <c r="C14" s="21">
         <f>$G14</f>
         <v/>
@@ -36872,8 +36945,8 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="96" t="n"/>
-      <c r="B16" s="96" t="n"/>
+      <c r="A16" s="97" t="n"/>
+      <c r="B16" s="97" t="n"/>
       <c r="C16" s="21">
         <f>$G16</f>
         <v/>
@@ -36886,8 +36959,8 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="96" t="n"/>
-      <c r="B17" s="96" t="n"/>
+      <c r="A17" s="97" t="n"/>
+      <c r="B17" s="97" t="n"/>
       <c r="C17" s="21">
         <f>$G17</f>
         <v/>
@@ -36900,8 +36973,8 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="96" t="n"/>
-      <c r="B18" s="96" t="n"/>
+      <c r="A18" s="97" t="n"/>
+      <c r="B18" s="97" t="n"/>
       <c r="C18" s="21">
         <f>$G18</f>
         <v/>
@@ -36914,8 +36987,8 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="97" t="n"/>
-      <c r="B19" s="97" t="n"/>
+      <c r="A19" s="98" t="n"/>
+      <c r="B19" s="98" t="n"/>
       <c r="C19" s="21">
         <f>$G19</f>
         <v/>
@@ -36946,8 +37019,8 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="96" t="n"/>
-      <c r="B21" s="96" t="n"/>
+      <c r="A21" s="97" t="n"/>
+      <c r="B21" s="97" t="n"/>
       <c r="C21" s="21">
         <f>$G21</f>
         <v/>
@@ -36960,8 +37033,8 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="96" t="n"/>
-      <c r="B22" s="96" t="n"/>
+      <c r="A22" s="97" t="n"/>
+      <c r="B22" s="97" t="n"/>
       <c r="C22" s="21">
         <f>$G22</f>
         <v/>
@@ -36974,8 +37047,8 @@
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="96" t="n"/>
-      <c r="B23" s="96" t="n"/>
+      <c r="A23" s="97" t="n"/>
+      <c r="B23" s="97" t="n"/>
       <c r="C23" s="21">
         <f>$G23</f>
         <v/>
@@ -36988,8 +37061,8 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="97" t="n"/>
-      <c r="B24" s="97" t="n"/>
+      <c r="A24" s="98" t="n"/>
+      <c r="B24" s="98" t="n"/>
       <c r="C24" s="21">
         <f>$G24</f>
         <v/>
@@ -37023,8 +37096,8 @@
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="96" t="n"/>
-      <c r="B26" s="96" t="n"/>
+      <c r="A26" s="97" t="n"/>
+      <c r="B26" s="97" t="n"/>
       <c r="C26" s="21">
         <f>$G26</f>
         <v/>
@@ -37037,8 +37110,8 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="96" t="n"/>
-      <c r="B27" s="96" t="n"/>
+      <c r="A27" s="97" t="n"/>
+      <c r="B27" s="97" t="n"/>
       <c r="C27" s="21">
         <f>$G27</f>
         <v/>
@@ -37051,8 +37124,8 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="96" t="n"/>
-      <c r="B28" s="96" t="n"/>
+      <c r="A28" s="97" t="n"/>
+      <c r="B28" s="97" t="n"/>
       <c r="C28" s="21">
         <f>$G28</f>
         <v/>
@@ -37065,8 +37138,8 @@
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="97" t="n"/>
-      <c r="B29" s="97" t="n"/>
+      <c r="A29" s="98" t="n"/>
+      <c r="B29" s="98" t="n"/>
       <c r="C29" s="21">
         <f>$G29</f>
         <v/>
@@ -37100,8 +37173,8 @@
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="96" t="n"/>
-      <c r="B31" s="96" t="n"/>
+      <c r="A31" s="97" t="n"/>
+      <c r="B31" s="97" t="n"/>
       <c r="C31" s="21">
         <f>$G31</f>
         <v/>
@@ -37114,8 +37187,8 @@
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="96" t="n"/>
-      <c r="B32" s="96" t="n"/>
+      <c r="A32" s="97" t="n"/>
+      <c r="B32" s="97" t="n"/>
       <c r="C32" s="21">
         <f>$G32</f>
         <v/>
@@ -37128,8 +37201,8 @@
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="96" t="n"/>
-      <c r="B33" s="96" t="n"/>
+      <c r="A33" s="97" t="n"/>
+      <c r="B33" s="97" t="n"/>
       <c r="C33" s="21">
         <f>$G33</f>
         <v/>
@@ -37142,8 +37215,8 @@
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="97" t="n"/>
-      <c r="B34" s="97" t="n"/>
+      <c r="A34" s="98" t="n"/>
+      <c r="B34" s="98" t="n"/>
       <c r="C34" s="21">
         <f>$G34</f>
         <v/>
@@ -37177,8 +37250,8 @@
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="96" t="n"/>
-      <c r="B36" s="96" t="n"/>
+      <c r="A36" s="97" t="n"/>
+      <c r="B36" s="97" t="n"/>
       <c r="C36" s="21">
         <f>$G36</f>
         <v/>
@@ -37191,8 +37264,8 @@
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="96" t="n"/>
-      <c r="B37" s="96" t="n"/>
+      <c r="A37" s="97" t="n"/>
+      <c r="B37" s="97" t="n"/>
       <c r="C37" s="21">
         <f>$G37</f>
         <v/>
@@ -37205,8 +37278,8 @@
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="96" t="n"/>
-      <c r="B38" s="96" t="n"/>
+      <c r="A38" s="97" t="n"/>
+      <c r="B38" s="97" t="n"/>
       <c r="C38" s="21">
         <f>$G38</f>
         <v/>
@@ -37219,8 +37292,8 @@
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="97" t="n"/>
-      <c r="B39" s="97" t="n"/>
+      <c r="A39" s="98" t="n"/>
+      <c r="B39" s="98" t="n"/>
       <c r="C39" s="21">
         <f>$G39</f>
         <v/>
@@ -37254,8 +37327,8 @@
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="96" t="n"/>
-      <c r="B41" s="96" t="n"/>
+      <c r="A41" s="97" t="n"/>
+      <c r="B41" s="97" t="n"/>
       <c r="C41" s="21">
         <f>$G41</f>
         <v/>
@@ -37268,8 +37341,8 @@
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="96" t="n"/>
-      <c r="B42" s="96" t="n"/>
+      <c r="A42" s="97" t="n"/>
+      <c r="B42" s="97" t="n"/>
       <c r="C42" s="21">
         <f>$G42</f>
         <v/>
@@ -37282,8 +37355,8 @@
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="96" t="n"/>
-      <c r="B43" s="96" t="n"/>
+      <c r="A43" s="97" t="n"/>
+      <c r="B43" s="97" t="n"/>
       <c r="C43" s="21">
         <f>$G43</f>
         <v/>
@@ -37296,8 +37369,8 @@
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="97" t="n"/>
-      <c r="B44" s="97" t="n"/>
+      <c r="A44" s="98" t="n"/>
+      <c r="B44" s="98" t="n"/>
       <c r="C44" s="21">
         <f>$G44</f>
         <v/>
@@ -37331,8 +37404,8 @@
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="96" t="n"/>
-      <c r="B46" s="96" t="n"/>
+      <c r="A46" s="97" t="n"/>
+      <c r="B46" s="97" t="n"/>
       <c r="C46" s="21">
         <f>$G46</f>
         <v/>
@@ -37345,8 +37418,8 @@
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="96" t="n"/>
-      <c r="B47" s="96" t="n"/>
+      <c r="A47" s="97" t="n"/>
+      <c r="B47" s="97" t="n"/>
       <c r="C47" s="21">
         <f>$G47</f>
         <v/>
@@ -37359,8 +37432,8 @@
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="96" t="n"/>
-      <c r="B48" s="96" t="n"/>
+      <c r="A48" s="97" t="n"/>
+      <c r="B48" s="97" t="n"/>
       <c r="C48" s="21">
         <f>$G48</f>
         <v/>
@@ -37373,8 +37446,8 @@
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="97" t="n"/>
-      <c r="B49" s="97" t="n"/>
+      <c r="A49" s="98" t="n"/>
+      <c r="B49" s="98" t="n"/>
       <c r="C49" s="21">
         <f>$G49</f>
         <v/>
@@ -37408,8 +37481,8 @@
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="96" t="n"/>
-      <c r="B51" s="96" t="n"/>
+      <c r="A51" s="97" t="n"/>
+      <c r="B51" s="97" t="n"/>
       <c r="C51" s="21">
         <f>$G51</f>
         <v/>
@@ -37422,8 +37495,8 @@
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="96" t="n"/>
-      <c r="B52" s="96" t="n"/>
+      <c r="A52" s="97" t="n"/>
+      <c r="B52" s="97" t="n"/>
       <c r="C52" s="21">
         <f>$G52</f>
         <v/>
@@ -37436,8 +37509,8 @@
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="96" t="n"/>
-      <c r="B53" s="96" t="n"/>
+      <c r="A53" s="97" t="n"/>
+      <c r="B53" s="97" t="n"/>
       <c r="C53" s="21">
         <f>$G53</f>
         <v/>
@@ -37450,8 +37523,8 @@
       </c>
     </row>
     <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="97" t="n"/>
-      <c r="B54" s="97" t="n"/>
+      <c r="A54" s="98" t="n"/>
+      <c r="B54" s="98" t="n"/>
       <c r="C54" s="21">
         <f>$G54</f>
         <v/>
@@ -37485,8 +37558,8 @@
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="96" t="n"/>
-      <c r="B56" s="96" t="n"/>
+      <c r="A56" s="97" t="n"/>
+      <c r="B56" s="97" t="n"/>
       <c r="C56" s="21">
         <f>$G56</f>
         <v/>
@@ -37499,8 +37572,8 @@
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="96" t="n"/>
-      <c r="B57" s="96" t="n"/>
+      <c r="A57" s="97" t="n"/>
+      <c r="B57" s="97" t="n"/>
       <c r="C57" s="21">
         <f>$G57</f>
         <v/>
@@ -37513,8 +37586,8 @@
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="96" t="n"/>
-      <c r="B58" s="96" t="n"/>
+      <c r="A58" s="97" t="n"/>
+      <c r="B58" s="97" t="n"/>
       <c r="C58" s="21">
         <f>$G58</f>
         <v/>
@@ -37527,8 +37600,8 @@
       </c>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="97" t="n"/>
-      <c r="B59" s="97" t="n"/>
+      <c r="A59" s="98" t="n"/>
+      <c r="B59" s="98" t="n"/>
       <c r="C59" s="21">
         <f>$G59</f>
         <v/>
@@ -37562,8 +37635,8 @@
       </c>
     </row>
     <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="96" t="n"/>
-      <c r="B61" s="96" t="n"/>
+      <c r="A61" s="97" t="n"/>
+      <c r="B61" s="97" t="n"/>
       <c r="C61" s="21">
         <f>$G61</f>
         <v/>
@@ -37576,8 +37649,8 @@
       </c>
     </row>
     <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="96" t="n"/>
-      <c r="B62" s="96" t="n"/>
+      <c r="A62" s="97" t="n"/>
+      <c r="B62" s="97" t="n"/>
       <c r="C62" s="21">
         <f>$G62</f>
         <v/>
@@ -37590,8 +37663,8 @@
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="96" t="n"/>
-      <c r="B63" s="96" t="n"/>
+      <c r="A63" s="97" t="n"/>
+      <c r="B63" s="97" t="n"/>
       <c r="C63" s="21">
         <f>$G63</f>
         <v/>
@@ -37604,8 +37677,8 @@
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="97" t="n"/>
-      <c r="B64" s="97" t="n"/>
+      <c r="A64" s="98" t="n"/>
+      <c r="B64" s="98" t="n"/>
       <c r="C64" s="21">
         <f>$G64</f>
         <v/>
@@ -37639,8 +37712,8 @@
       </c>
     </row>
     <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="96" t="n"/>
-      <c r="B66" s="96" t="n"/>
+      <c r="A66" s="97" t="n"/>
+      <c r="B66" s="97" t="n"/>
       <c r="C66" s="21">
         <f>$G66</f>
         <v/>
@@ -37653,8 +37726,8 @@
       </c>
     </row>
     <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="96" t="n"/>
-      <c r="B67" s="96" t="n"/>
+      <c r="A67" s="97" t="n"/>
+      <c r="B67" s="97" t="n"/>
       <c r="C67" s="21">
         <f>$G67</f>
         <v/>
@@ -37667,8 +37740,8 @@
       </c>
     </row>
     <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="96" t="n"/>
-      <c r="B68" s="96" t="n"/>
+      <c r="A68" s="97" t="n"/>
+      <c r="B68" s="97" t="n"/>
       <c r="C68" s="21">
         <f>$G68</f>
         <v/>
@@ -37681,8 +37754,8 @@
       </c>
     </row>
     <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="97" t="n"/>
-      <c r="B69" s="97" t="n"/>
+      <c r="A69" s="98" t="n"/>
+      <c r="B69" s="98" t="n"/>
       <c r="C69" s="21">
         <f>$G69</f>
         <v/>
@@ -37716,8 +37789,8 @@
       </c>
     </row>
     <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="96" t="n"/>
-      <c r="B71" s="96" t="n"/>
+      <c r="A71" s="97" t="n"/>
+      <c r="B71" s="97" t="n"/>
       <c r="C71" s="21">
         <f>$G71</f>
         <v/>
@@ -37730,8 +37803,8 @@
       </c>
     </row>
     <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="96" t="n"/>
-      <c r="B72" s="96" t="n"/>
+      <c r="A72" s="97" t="n"/>
+      <c r="B72" s="97" t="n"/>
       <c r="C72" s="21">
         <f>$G72</f>
         <v/>
@@ -37744,8 +37817,8 @@
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="96" t="n"/>
-      <c r="B73" s="96" t="n"/>
+      <c r="A73" s="97" t="n"/>
+      <c r="B73" s="97" t="n"/>
       <c r="C73" s="21">
         <f>$G73</f>
         <v/>
@@ -37758,8 +37831,8 @@
       </c>
     </row>
     <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="97" t="n"/>
-      <c r="B74" s="97" t="n"/>
+      <c r="A74" s="98" t="n"/>
+      <c r="B74" s="98" t="n"/>
       <c r="C74" s="21">
         <f>$G74</f>
         <v/>
@@ -37793,8 +37866,8 @@
       </c>
     </row>
     <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="96" t="n"/>
-      <c r="B76" s="96" t="n"/>
+      <c r="A76" s="97" t="n"/>
+      <c r="B76" s="97" t="n"/>
       <c r="C76" s="21">
         <f>$G76</f>
         <v/>
@@ -37807,8 +37880,8 @@
       </c>
     </row>
     <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="96" t="n"/>
-      <c r="B77" s="96" t="n"/>
+      <c r="A77" s="97" t="n"/>
+      <c r="B77" s="97" t="n"/>
       <c r="C77" s="21">
         <f>$G77</f>
         <v/>
@@ -37821,8 +37894,8 @@
       </c>
     </row>
     <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="96" t="n"/>
-      <c r="B78" s="96" t="n"/>
+      <c r="A78" s="97" t="n"/>
+      <c r="B78" s="97" t="n"/>
       <c r="C78" s="21">
         <f>$G78</f>
         <v/>
@@ -37835,8 +37908,8 @@
       </c>
     </row>
     <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="97" t="n"/>
-      <c r="B79" s="97" t="n"/>
+      <c r="A79" s="98" t="n"/>
+      <c r="B79" s="98" t="n"/>
       <c r="C79" s="21">
         <f>$G79</f>
         <v/>
@@ -37870,8 +37943,8 @@
       </c>
     </row>
     <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="96" t="n"/>
-      <c r="B81" s="96" t="n"/>
+      <c r="A81" s="97" t="n"/>
+      <c r="B81" s="97" t="n"/>
       <c r="C81" s="21">
         <f>$G81</f>
         <v/>
@@ -37884,8 +37957,8 @@
       </c>
     </row>
     <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="96" t="n"/>
-      <c r="B82" s="96" t="n"/>
+      <c r="A82" s="97" t="n"/>
+      <c r="B82" s="97" t="n"/>
       <c r="C82" s="21">
         <f>$G82</f>
         <v/>
@@ -37898,8 +37971,8 @@
       </c>
     </row>
     <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="96" t="n"/>
-      <c r="B83" s="96" t="n"/>
+      <c r="A83" s="97" t="n"/>
+      <c r="B83" s="97" t="n"/>
       <c r="C83" s="21">
         <f>$G83</f>
         <v/>
@@ -37912,8 +37985,8 @@
       </c>
     </row>
     <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="97" t="n"/>
-      <c r="B84" s="97" t="n"/>
+      <c r="A84" s="98" t="n"/>
+      <c r="B84" s="98" t="n"/>
       <c r="C84" s="21">
         <f>$G84</f>
         <v/>
@@ -37947,8 +38020,8 @@
       </c>
     </row>
     <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="96" t="n"/>
-      <c r="B86" s="96" t="n"/>
+      <c r="A86" s="97" t="n"/>
+      <c r="B86" s="97" t="n"/>
       <c r="C86" s="21">
         <f>$G86</f>
         <v/>
@@ -37961,8 +38034,8 @@
       </c>
     </row>
     <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="96" t="n"/>
-      <c r="B87" s="96" t="n"/>
+      <c r="A87" s="97" t="n"/>
+      <c r="B87" s="97" t="n"/>
       <c r="C87" s="21">
         <f>$G87</f>
         <v/>
@@ -37975,8 +38048,8 @@
       </c>
     </row>
     <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="96" t="n"/>
-      <c r="B88" s="96" t="n"/>
+      <c r="A88" s="97" t="n"/>
+      <c r="B88" s="97" t="n"/>
       <c r="C88" s="21">
         <f>$G88</f>
         <v/>
@@ -37989,8 +38062,8 @@
       </c>
     </row>
     <row r="89" ht="24" customHeight="1">
-      <c r="A89" s="97" t="n"/>
-      <c r="B89" s="97" t="n"/>
+      <c r="A89" s="98" t="n"/>
+      <c r="B89" s="98" t="n"/>
       <c r="C89" s="21">
         <f>$G89</f>
         <v/>
@@ -38021,8 +38094,8 @@
       </c>
     </row>
     <row r="91" ht="24" customHeight="1">
-      <c r="A91" s="96" t="n"/>
-      <c r="B91" s="96" t="n"/>
+      <c r="A91" s="97" t="n"/>
+      <c r="B91" s="97" t="n"/>
       <c r="C91" s="21">
         <f>$G91</f>
         <v/>
@@ -38035,8 +38108,8 @@
       </c>
     </row>
     <row r="92" ht="24" customHeight="1">
-      <c r="A92" s="96" t="n"/>
-      <c r="B92" s="96" t="n"/>
+      <c r="A92" s="97" t="n"/>
+      <c r="B92" s="97" t="n"/>
       <c r="C92" s="21">
         <f>$G92</f>
         <v/>
@@ -38049,8 +38122,8 @@
       </c>
     </row>
     <row r="93" ht="24" customHeight="1">
-      <c r="A93" s="96" t="n"/>
-      <c r="B93" s="96" t="n"/>
+      <c r="A93" s="97" t="n"/>
+      <c r="B93" s="97" t="n"/>
       <c r="C93" s="21">
         <f>$G93</f>
         <v/>
@@ -38063,8 +38136,8 @@
       </c>
     </row>
     <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="96" t="n"/>
-      <c r="B94" s="96" t="n"/>
+      <c r="A94" s="97" t="n"/>
+      <c r="B94" s="97" t="n"/>
       <c r="C94" s="21">
         <f>$G94</f>
         <v/>
@@ -38077,8 +38150,8 @@
       </c>
     </row>
     <row r="95" ht="24" customHeight="1">
-      <c r="A95" s="96" t="n"/>
-      <c r="B95" s="96" t="n"/>
+      <c r="A95" s="97" t="n"/>
+      <c r="B95" s="97" t="n"/>
       <c r="C95" s="21">
         <f>$G95</f>
         <v/>
@@ -38091,8 +38164,8 @@
       </c>
     </row>
     <row r="96" ht="24" customHeight="1">
-      <c r="A96" s="96" t="n"/>
-      <c r="B96" s="96" t="n"/>
+      <c r="A96" s="97" t="n"/>
+      <c r="B96" s="97" t="n"/>
       <c r="C96" s="21">
         <f>$G96</f>
         <v/>
@@ -38105,8 +38178,8 @@
       </c>
     </row>
     <row r="97" ht="24" customHeight="1">
-      <c r="A97" s="96" t="n"/>
-      <c r="B97" s="96" t="n"/>
+      <c r="A97" s="97" t="n"/>
+      <c r="B97" s="97" t="n"/>
       <c r="C97" s="21">
         <f>$G97</f>
         <v/>
@@ -38119,8 +38192,8 @@
       </c>
     </row>
     <row r="98" ht="24" customHeight="1">
-      <c r="A98" s="96" t="n"/>
-      <c r="B98" s="96" t="n"/>
+      <c r="A98" s="97" t="n"/>
+      <c r="B98" s="97" t="n"/>
       <c r="C98" s="21">
         <f>$G98</f>
         <v/>
@@ -38133,8 +38206,8 @@
       </c>
     </row>
     <row r="99" ht="24" customHeight="1">
-      <c r="A99" s="96" t="n"/>
-      <c r="B99" s="96" t="n"/>
+      <c r="A99" s="97" t="n"/>
+      <c r="B99" s="97" t="n"/>
       <c r="C99" s="21">
         <f>$G99</f>
         <v/>
@@ -38147,8 +38220,8 @@
       </c>
     </row>
     <row r="100" ht="24" customHeight="1">
-      <c r="A100" s="96" t="n"/>
-      <c r="B100" s="96" t="n"/>
+      <c r="A100" s="97" t="n"/>
+      <c r="B100" s="97" t="n"/>
       <c r="C100" s="21">
         <f>$G100</f>
         <v/>
@@ -38161,8 +38234,8 @@
       </c>
     </row>
     <row r="101" ht="24" customHeight="1">
-      <c r="A101" s="96" t="n"/>
-      <c r="B101" s="96" t="n"/>
+      <c r="A101" s="97" t="n"/>
+      <c r="B101" s="97" t="n"/>
       <c r="C101" s="21">
         <f>$G101</f>
         <v/>
@@ -38175,8 +38248,8 @@
       </c>
     </row>
     <row r="102" ht="24" customHeight="1">
-      <c r="A102" s="96" t="n"/>
-      <c r="B102" s="96" t="n"/>
+      <c r="A102" s="97" t="n"/>
+      <c r="B102" s="97" t="n"/>
       <c r="C102" s="21">
         <f>$G102</f>
         <v/>
@@ -38189,8 +38262,8 @@
       </c>
     </row>
     <row r="103" ht="24" customHeight="1">
-      <c r="A103" s="97" t="n"/>
-      <c r="B103" s="97" t="n"/>
+      <c r="A103" s="98" t="n"/>
+      <c r="B103" s="98" t="n"/>
       <c r="C103" s="21">
         <f>$G103</f>
         <v/>
@@ -38218,9 +38291,9 @@
     <mergeCell ref="C40:E40"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C21:E21"/>
+    <mergeCell ref="B5:B9"/>
     <mergeCell ref="C51:E51"/>
     <mergeCell ref="C95:E95"/>
-    <mergeCell ref="B5:B9"/>
     <mergeCell ref="C60:E60"/>
     <mergeCell ref="C71:E71"/>
     <mergeCell ref="C23:E23"/>
